--- a/03_Outputs/Rio_Grande/06_Desarrollo_Rural/desarrollo_rural.xlsx
+++ b/03_Outputs/Rio_Grande/06_Desarrollo_Rural/desarrollo_rural.xlsx
@@ -81,7 +81,7 @@
     <numFmt numFmtId="218" formatCode="#,##0.00"/>
     <numFmt numFmtId="219" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,23 +91,162 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -127,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -148,9 +287,13 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="178" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="179" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="180" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="181" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="182" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="183" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="184" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="185" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="186" xfId="0"/>
@@ -158,35 +301,56 @@
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="188" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="189" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="191" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="7" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="193" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="194" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="195" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="7" fontId="8" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="196" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="197" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="9" numFmtId="197" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="198" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="199" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="9" numFmtId="199" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="200" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="201" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="9" numFmtId="201" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="202" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="203" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="9" numFmtId="203" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="204" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="205" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="9" numFmtId="205" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="206" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="207" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="9" numFmtId="207" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="208" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="209" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="9" numFmtId="209" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="210" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="211" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="9" numFmtId="211" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="8" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="212" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="213" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="11" numFmtId="213" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="214" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="215" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="11" numFmtId="215" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="216" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="217" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="11" numFmtId="217" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="218" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="219" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="11" numFmtId="219" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="9" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="10" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="11" fontId="14" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="12" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="13" fontId="16" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -515,17 +679,17 @@
   <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="7" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="6" max="7" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -627,11 +791,15 @@
       <c r="J2" s="14">
         <v>911</v>
       </c>
-      <c r="K2" s="16">
-        <v>0</v>
-      </c>
-      <c r="L2" s="18">
-        <v>36040</v>
+      <c r="K2" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L2" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -715,11 +883,15 @@
       <c r="J4" s="14">
         <v>827</v>
       </c>
-      <c r="K4" s="16">
-        <v>0</v>
-      </c>
-      <c r="L4" s="18">
-        <v>54725</v>
+      <c r="K4" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -759,11 +931,15 @@
       <c r="J5" s="14">
         <v>1607</v>
       </c>
-      <c r="K5" s="16">
-        <v>0</v>
-      </c>
-      <c r="L5" s="18">
-        <v>86818</v>
+      <c r="K5" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -853,7 +1029,7 @@
         <v>99695</v>
       </c>
       <c r="L7" s="19">
-        <v>456163</v>
+        <v>278580</v>
       </c>
     </row>
     <row r="8">
@@ -899,7 +1075,7 @@
         <v>99695</v>
       </c>
       <c r="L8" s="19">
-        <v>689657</v>
+        <v>278580</v>
       </c>
     </row>
     <row r="9">
@@ -945,7 +1121,7 @@
         <v>606143</v>
       </c>
       <c r="L9" s="19">
-        <v>4007472</v>
+        <v>1101682</v>
       </c>
     </row>
     <row r="10">
@@ -3108,28 +3284,29 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="79" t="inlineStr">
         <is>
           <t>ciclo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="79" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="79" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
@@ -3347,40 +3524,40 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="3" max="4" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="3" max="4" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="81" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="81" t="inlineStr">
         <is>
           <t>anio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="81" t="inlineStr">
         <is>
           <t>prod_perm</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="81" t="inlineStr">
         <is>
           <t>prod_tran</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="81" t="inlineStr">
         <is>
           <t>prod_total</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="81" t="inlineStr">
         <is>
           <t>pct_prod_prov</t>
         </is>
@@ -3508,35 +3685,35 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="83" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="83" t="inlineStr">
         <is>
           <t>anio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="83" t="inlineStr">
         <is>
           <t>produccion_cultivo</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="83" t="inlineStr">
         <is>
           <t>area_cosechada</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="83" t="inlineStr">
         <is>
           <t>rendimiento</t>
         </is>
@@ -3649,47 +3826,47 @@
   <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="21" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="21" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="21" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="21" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="21" t="inlineStr">
         <is>
           <t>Total especies pecuarias</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="21" t="inlineStr">
         <is>
           <t>Participación en el total provincial (%)</t>
         </is>
@@ -3714,14 +3891,18 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="22">
         <v>2019</v>
       </c>
-      <c r="F2" s="21">
-        <v>36040</v>
-      </c>
-      <c r="G2" s="22">
-        <v>0.0790068462369811</v>
+      <c r="F2" s="23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -3743,14 +3924,14 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="22">
         <v>2019</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="23">
         <v>109257</v>
       </c>
-      <c r="G3" s="22">
-        <v>0.239513068793392</v>
+      <c r="G3" s="24">
+        <v>0.392192547921602</v>
       </c>
     </row>
     <row r="4">
@@ -3772,14 +3953,18 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="22">
         <v>2019</v>
       </c>
-      <c r="F4" s="21">
-        <v>54725</v>
-      </c>
-      <c r="G4" s="22">
-        <v>0.119968081584872</v>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3801,14 +3986,18 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="22">
         <v>2019</v>
       </c>
-      <c r="F5" s="21">
-        <v>86818</v>
-      </c>
-      <c r="G5" s="22">
-        <v>0.190322318995622</v>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -3830,14 +4019,14 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="22">
         <v>2019</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="23">
         <v>169323</v>
       </c>
-      <c r="G6" s="22">
-        <v>0.371189684389133</v>
+      <c r="G6" s="24">
+        <v>0.607807452078398</v>
       </c>
     </row>
     <row r="7">
@@ -3859,13 +4048,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="22">
         <v>2020</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="23">
         <v>61590</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="24">
         <v>0.0640158818424185</v>
       </c>
     </row>
@@ -3888,13 +4077,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="22">
         <v>2020</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="23">
         <v>307857</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="24">
         <v>0.319982746165959</v>
       </c>
     </row>
@@ -3917,13 +4106,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="22">
         <v>2020</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="23">
         <v>103771</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="24">
         <v>0.107858289895594</v>
       </c>
     </row>
@@ -3946,13 +4135,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="22">
         <v>2020</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="23">
         <v>157075</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="24">
         <v>0.16326180614382</v>
       </c>
     </row>
@@ -3975,13 +4164,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="22">
         <v>2020</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="23">
         <v>331812</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="24">
         <v>0.344881275952209</v>
       </c>
     </row>
@@ -4004,13 +4193,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="22">
         <v>2021</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="23">
         <v>39014</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="24">
         <v>0.0427652384183417</v>
       </c>
     </row>
@@ -4033,13 +4222,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="22">
         <v>2021</v>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="23">
         <v>293169</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="24">
         <v>0.321357517349331</v>
       </c>
     </row>
@@ -4062,13 +4251,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="22">
         <v>2021</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="23">
         <v>80556</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="24">
         <v>0.0883015467787956</v>
       </c>
     </row>
@@ -4091,13 +4280,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="22">
         <v>2021</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="23">
         <v>130169</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="24">
         <v>0.142684890543833</v>
       </c>
     </row>
@@ -4120,13 +4309,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="22">
         <v>2021</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="23">
         <v>369375</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="24">
         <v>0.404890806909698</v>
       </c>
     </row>
@@ -4149,13 +4338,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="22">
         <v>2022</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="23">
         <v>56888</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="24">
         <v>0.0594335384518946</v>
       </c>
     </row>
@@ -4178,13 +4367,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E18" s="20">
+      <c r="E18" s="22">
         <v>2022</v>
       </c>
-      <c r="F18" s="21">
+      <c r="F18" s="23">
         <v>235660</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="24">
         <v>0.246204958366852</v>
       </c>
     </row>
@@ -4207,13 +4396,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="22">
         <v>2022</v>
       </c>
-      <c r="F19" s="21">
+      <c r="F19" s="23">
         <v>119647</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="24">
         <v>0.125000783559869</v>
       </c>
     </row>
@@ -4236,13 +4425,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="22">
         <v>2022</v>
       </c>
-      <c r="F20" s="21">
+      <c r="F20" s="23">
         <v>195269</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="24">
         <v>0.204006602797831</v>
       </c>
     </row>
@@ -4265,13 +4454,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="22">
         <v>2022</v>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="23">
         <v>349706</v>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="24">
         <v>0.365354116823553</v>
       </c>
     </row>
@@ -4294,13 +4483,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="22">
         <v>2023</v>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="23">
         <v>54285</v>
       </c>
-      <c r="G22" s="22">
+      <c r="G22" s="24">
         <v>0.0570649174537599</v>
       </c>
     </row>
@@ -4323,13 +4512,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="22">
         <v>2023</v>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="23">
         <v>234133</v>
       </c>
-      <c r="G23" s="22">
+      <c r="G23" s="24">
         <v>0.246122875899441</v>
       </c>
     </row>
@@ -4352,13 +4541,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="22">
         <v>2023</v>
       </c>
-      <c r="F24" s="21">
+      <c r="F24" s="23">
         <v>118727</v>
       </c>
-      <c r="G24" s="22">
+      <c r="G24" s="24">
         <v>0.124806971622595</v>
       </c>
     </row>
@@ -4381,13 +4570,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E25" s="20">
+      <c r="E25" s="22">
         <v>2023</v>
       </c>
-      <c r="F25" s="21">
+      <c r="F25" s="23">
         <v>191312</v>
       </c>
-      <c r="G25" s="22">
+      <c r="G25" s="24">
         <v>0.201109026211913</v>
       </c>
     </row>
@@ -4410,13 +4599,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E26" s="20">
+      <c r="E26" s="22">
         <v>2023</v>
       </c>
-      <c r="F26" s="21">
+      <c r="F26" s="23">
         <v>352828</v>
       </c>
-      <c r="G26" s="22">
+      <c r="G26" s="24">
         <v>0.370896208812291</v>
       </c>
     </row>
@@ -4439,13 +4628,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E27" s="20">
+      <c r="E27" s="22">
         <v>2024</v>
       </c>
-      <c r="F27" s="21">
+      <c r="F27" s="23">
         <v>37173</v>
       </c>
-      <c r="G27" s="22">
+      <c r="G27" s="24">
         <v>0.0306350006922605</v>
       </c>
     </row>
@@ -4468,13 +4657,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E28" s="20">
+      <c r="E28" s="22">
         <v>2024</v>
       </c>
-      <c r="F28" s="21">
+      <c r="F28" s="23">
         <v>377846</v>
       </c>
-      <c r="G28" s="22">
+      <c r="G28" s="24">
         <v>0.311390322857124</v>
       </c>
     </row>
@@ -4497,13 +4686,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E29" s="20">
+      <c r="E29" s="22">
         <v>2024</v>
       </c>
-      <c r="F29" s="21">
+      <c r="F29" s="23">
         <v>128571</v>
       </c>
-      <c r="G29" s="22">
+      <c r="G29" s="24">
         <v>0.105957890781068</v>
       </c>
     </row>
@@ -4526,13 +4715,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E30" s="20">
+      <c r="E30" s="22">
         <v>2024</v>
       </c>
-      <c r="F30" s="21">
+      <c r="F30" s="23">
         <v>218448</v>
       </c>
-      <c r="G30" s="22">
+      <c r="G30" s="24">
         <v>0.180027294843648</v>
       </c>
     </row>
@@ -4555,13 +4744,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E31" s="20">
+      <c r="E31" s="22">
         <v>2024</v>
       </c>
-      <c r="F31" s="21">
+      <c r="F31" s="23">
         <v>451378</v>
       </c>
-      <c r="G31" s="22">
+      <c r="G31" s="24">
         <v>0.3719894908259</v>
       </c>
     </row>
@@ -4584,13 +4773,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="22">
         <v>2025</v>
       </c>
-      <c r="F32" s="21">
+      <c r="F32" s="23">
         <v>65268</v>
       </c>
-      <c r="G32" s="22">
+      <c r="G32" s="24">
         <v>0.050707888903823</v>
       </c>
     </row>
@@ -4613,13 +4802,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E33" s="20">
+      <c r="E33" s="22">
         <v>2025</v>
       </c>
-      <c r="F33" s="21">
+      <c r="F33" s="23">
         <v>382452</v>
       </c>
-      <c r="G33" s="22">
+      <c r="G33" s="24">
         <v>0.297133871530381</v>
       </c>
     </row>
@@ -4642,13 +4831,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E34" s="20">
+      <c r="E34" s="22">
         <v>2025</v>
       </c>
-      <c r="F34" s="21">
+      <c r="F34" s="23">
         <v>133906</v>
       </c>
-      <c r="G34" s="22">
+      <c r="G34" s="24">
         <v>0.104033991719607</v>
       </c>
     </row>
@@ -4671,13 +4860,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E35" s="20">
+      <c r="E35" s="22">
         <v>2025</v>
       </c>
-      <c r="F35" s="21">
+      <c r="F35" s="23">
         <v>204303</v>
       </c>
-      <c r="G35" s="22">
+      <c r="G35" s="24">
         <v>0.158726693428905</v>
       </c>
     </row>
@@ -4700,13 +4889,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E36" s="20">
+      <c r="E36" s="22">
         <v>2025</v>
       </c>
-      <c r="F36" s="21">
+      <c r="F36" s="23">
         <v>501208</v>
       </c>
-      <c r="G36" s="22">
+      <c r="G36" s="24">
         <v>0.389397554417284</v>
       </c>
     </row>
@@ -4722,70 +4911,69 @@
   <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="8" max="9" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="7" max="9" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="26" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
         <is>
           <t>Bovinos (%)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="26" t="inlineStr">
         <is>
           <t>Búfalos (%)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="26" t="inlineStr">
         <is>
           <t>Caprinos (%)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="26" t="inlineStr">
         <is>
           <t>Ovinos (%)</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="26" t="inlineStr">
         <is>
           <t>Equinos (%)</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="26" t="inlineStr">
         <is>
           <t>Porcinos (%)</t>
         </is>
@@ -4810,26 +4998,38 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="23">
+      <c r="E2" s="27">
         <v>2019</v>
       </c>
-      <c r="F2" s="24">
-        <v>0.969034406215316</v>
-      </c>
-      <c r="G2" s="25">
-        <v>0.00086015538290788</v>
-      </c>
-      <c r="H2" s="26">
-        <v>0.00113762486126526</v>
-      </c>
-      <c r="I2" s="27">
-        <v>0.00369034406215316</v>
-      </c>
-      <c r="J2" s="28">
-        <v>0.0252774694783574</v>
-      </c>
-      <c r="K2" s="29">
-        <v>0</v>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H2" s="30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" s="31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J2" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K2" s="33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -4851,25 +5051,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="23">
+      <c r="E3" s="27">
         <v>2019</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="28">
         <v>0.312401036089221</v>
       </c>
-      <c r="G3" s="25">
+      <c r="G3" s="29">
         <v>0.0000091527316327558</v>
       </c>
-      <c r="H3" s="26">
+      <c r="H3" s="30">
         <v>0.000421025655106767</v>
       </c>
-      <c r="I3" s="27">
+      <c r="I3" s="31">
         <v>0.00170240808369258</v>
       </c>
-      <c r="J3" s="28">
+      <c r="J3" s="32">
         <v>0.0121090639501359</v>
       </c>
-      <c r="K3" s="29">
+      <c r="K3" s="33">
         <v>0.673357313490211</v>
       </c>
     </row>
@@ -4892,26 +5092,38 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="27">
         <v>2019</v>
       </c>
-      <c r="F4" s="24">
-        <v>0.980264961169484</v>
-      </c>
-      <c r="G4" s="25">
-        <v>0.0000182731841023298</v>
-      </c>
-      <c r="H4" s="26">
-        <v>0.000529922338967565</v>
-      </c>
-      <c r="I4" s="27">
-        <v>0.00407492005481955</v>
-      </c>
-      <c r="J4" s="28">
-        <v>0.0151119232526268</v>
-      </c>
-      <c r="K4" s="29">
-        <v>0</v>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H4" s="30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" s="31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" s="33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -4933,26 +5145,38 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="27">
         <v>2019</v>
       </c>
-      <c r="F5" s="24">
-        <v>0.975615655739593</v>
-      </c>
-      <c r="G5" s="25">
-        <v>0</v>
-      </c>
-      <c r="H5" s="26">
-        <v>0.00145131193992029</v>
-      </c>
-      <c r="I5" s="27">
-        <v>0.00442304591213804</v>
-      </c>
-      <c r="J5" s="28">
-        <v>0.0185099864083485</v>
-      </c>
-      <c r="K5" s="29">
-        <v>0</v>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H5" s="30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" s="31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" s="33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4974,25 +5198,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="27">
         <v>2019</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="28">
         <v>0.828800576413128</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="29">
         <v>0.00197846718992694</v>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="30">
         <v>0.00175994991820367</v>
       </c>
-      <c r="I6" s="27">
+      <c r="I6" s="31">
         <v>0.00341950000885881</v>
       </c>
-      <c r="J6" s="28">
+      <c r="J6" s="32">
         <v>0.00974468914441629</v>
       </c>
-      <c r="K6" s="29">
+      <c r="K6" s="33">
         <v>0.154296817325467</v>
       </c>
     </row>
@@ -5015,25 +5239,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="27">
         <v>2020</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="28">
         <v>0.587546679655788</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="29">
         <v>0.0000487092060399415</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="30">
         <v>0.000698165286572495</v>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="31">
         <v>0.00219191427179737</v>
       </c>
-      <c r="J7" s="28">
+      <c r="J7" s="32">
         <v>0.0137847053093035</v>
       </c>
-      <c r="K7" s="29">
+      <c r="K7" s="33">
         <v>0.395729826270498</v>
       </c>
     </row>
@@ -5056,25 +5280,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="27">
         <v>2020</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="28">
         <v>0.119643210971328</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="29">
         <v>0</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="30">
         <v>0.000162413068405136</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="31">
         <v>0.00058468704625849</v>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="32">
         <v>0.00450858677892658</v>
       </c>
-      <c r="K8" s="29">
+      <c r="K8" s="33">
         <v>0.875101102135082</v>
       </c>
     </row>
@@ -5097,25 +5321,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="27">
         <v>2020</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="28">
         <v>0.563172755394089</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="29">
         <v>0</v>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="30">
         <v>0.000260188299235817</v>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="31">
         <v>0.00192732073508013</v>
       </c>
-      <c r="J9" s="28">
+      <c r="J9" s="32">
         <v>0.00638906823679063</v>
       </c>
-      <c r="K9" s="29">
+      <c r="K9" s="33">
         <v>0.428250667334805</v>
       </c>
     </row>
@@ -5138,25 +5362,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="27">
         <v>2020</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="28">
         <v>0.583027216297947</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="29">
         <v>0.0000254655419385644</v>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="30">
         <v>0.000783065414610855</v>
       </c>
-      <c r="I10" s="27">
+      <c r="I10" s="31">
         <v>0.00241286009867897</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="32">
         <v>0.01046633773675</v>
       </c>
-      <c r="K10" s="29">
+      <c r="K10" s="33">
         <v>0.403285054910075</v>
       </c>
     </row>
@@ -5179,25 +5403,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="27">
         <v>2020</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="28">
         <v>0.464684821525442</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="29">
         <v>0.00000301375477680132</v>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="30">
         <v>0.0000271237929912119</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="31">
         <v>0.00165756512724073</v>
       </c>
-      <c r="J11" s="28">
+      <c r="J11" s="32">
         <v>0.00557544633708244</v>
       </c>
-      <c r="K11" s="29">
+      <c r="K11" s="33">
         <v>0.528052029462467</v>
       </c>
     </row>
@@ -5220,25 +5444,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="27">
         <v>2021</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="28">
         <v>0.89711385656431</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="29">
         <v>0.00012815912236633</v>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="30">
         <v>0.000717691085251448</v>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="31">
         <v>0.00276823704311273</v>
       </c>
-      <c r="J12" s="28">
+      <c r="J12" s="32">
         <v>0.0240426513559235</v>
       </c>
-      <c r="K12" s="29">
+      <c r="K12" s="33">
         <v>0.0752294048290357</v>
       </c>
     </row>
@@ -5261,25 +5485,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="27">
         <v>2021</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="28">
         <v>0.124709638467914</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="29">
         <v>0</v>
       </c>
-      <c r="H13" s="26">
+      <c r="H13" s="30">
         <v>0.000122796066432672</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="31">
         <v>0.00013644007381408</v>
       </c>
-      <c r="J13" s="28">
+      <c r="J13" s="32">
         <v>0.00473447056134857</v>
       </c>
-      <c r="K13" s="29">
+      <c r="K13" s="33">
         <v>0.87029665483049</v>
       </c>
     </row>
@@ -5302,25 +5526,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="27">
         <v>2021</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="28">
         <v>0.704379562043796</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="29">
         <v>0.000608272506082725</v>
       </c>
-      <c r="H14" s="26">
+      <c r="H14" s="30">
         <v>0.000546203883013059</v>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="31">
         <v>0.0000868960722975322</v>
       </c>
-      <c r="J14" s="28">
+      <c r="J14" s="32">
         <v>0.00993097969114653</v>
       </c>
-      <c r="K14" s="29">
+      <c r="K14" s="33">
         <v>0.284448085803665</v>
       </c>
     </row>
@@ -5343,25 +5567,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="27">
         <v>2021</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="28">
         <v>0.643233027833048</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="29">
         <v>0.000261198902964608</v>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="30">
         <v>0.000560809409306363</v>
       </c>
-      <c r="I15" s="27">
+      <c r="I15" s="31">
         <v>0.000868102236323549</v>
       </c>
-      <c r="J15" s="28">
+      <c r="J15" s="32">
         <v>0.0138742711398259</v>
       </c>
-      <c r="K15" s="29">
+      <c r="K15" s="33">
         <v>0.341202590478532</v>
       </c>
     </row>
@@ -5384,25 +5608,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="27">
         <v>2021</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="28">
         <v>0.416354653130288</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="29">
         <v>0.000360067681895093</v>
       </c>
-      <c r="H16" s="26">
+      <c r="H16" s="30">
         <v>0.000563113367174281</v>
       </c>
-      <c r="I16" s="27">
+      <c r="I16" s="31">
         <v>0.000982741116751269</v>
       </c>
-      <c r="J16" s="28">
+      <c r="J16" s="32">
         <v>0.00829238578680203</v>
       </c>
-      <c r="K16" s="29">
+      <c r="K16" s="33">
         <v>0.57344703891709</v>
       </c>
     </row>
@@ -5425,25 +5649,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="27">
         <v>2022</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="28">
         <v>0.682411053297708</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="29">
         <v>0.000210940795949937</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="30">
         <v>0.000404303192237379</v>
       </c>
-      <c r="I17" s="27">
+      <c r="I17" s="31">
         <v>0.00581845028828575</v>
       </c>
-      <c r="J17" s="28">
+      <c r="J17" s="32">
         <v>0.0346821825341021</v>
       </c>
-      <c r="K17" s="29">
+      <c r="K17" s="33">
         <v>0.276473069891717</v>
       </c>
     </row>
@@ -5466,25 +5690,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="27">
         <v>2022</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="28">
         <v>0.160812187049139</v>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="29">
         <v>0</v>
       </c>
-      <c r="H18" s="26">
+      <c r="H18" s="30">
         <v>0.000237630484596453</v>
       </c>
-      <c r="I18" s="27">
+      <c r="I18" s="31">
         <v>0.00168887380123907</v>
       </c>
-      <c r="J18" s="28">
+      <c r="J18" s="32">
         <v>0.00966222523975219</v>
       </c>
-      <c r="K18" s="29">
+      <c r="K18" s="33">
         <v>0.827599083425274</v>
       </c>
     </row>
@@ -5507,25 +5731,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="27">
         <v>2022</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="28">
         <v>0.4920390816318</v>
       </c>
-      <c r="G19" s="25">
+      <c r="G19" s="29">
         <v>0</v>
       </c>
-      <c r="H19" s="26">
+      <c r="H19" s="30">
         <v>0.00203097444983995</v>
       </c>
-      <c r="I19" s="27">
+      <c r="I19" s="31">
         <v>0.00431268648607989</v>
       </c>
-      <c r="J19" s="28">
+      <c r="J19" s="32">
         <v>0.011650939848053</v>
       </c>
-      <c r="K19" s="29">
+      <c r="K19" s="33">
         <v>0.489966317584227</v>
       </c>
     </row>
@@ -5548,25 +5772,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="27">
         <v>2022</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="28">
         <v>0.426375922445447</v>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="29">
         <v>0</v>
       </c>
-      <c r="H20" s="26">
+      <c r="H20" s="30">
         <v>0.000281662731923654</v>
       </c>
-      <c r="I20" s="27">
+      <c r="I20" s="31">
         <v>0.000604294588490749</v>
       </c>
-      <c r="J20" s="28">
+      <c r="J20" s="32">
         <v>0.0132330272598313</v>
       </c>
-      <c r="K20" s="29">
+      <c r="K20" s="33">
         <v>0.559505092974307</v>
       </c>
     </row>
@@ -5589,25 +5813,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="27">
         <v>2022</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="28">
         <v>0.477561151367148</v>
       </c>
-      <c r="G21" s="25">
+      <c r="G21" s="29">
         <v>0.000243061314361206</v>
       </c>
-      <c r="H21" s="26">
+      <c r="H21" s="30">
         <v>0.000563330340343031</v>
       </c>
-      <c r="I21" s="27">
+      <c r="I21" s="31">
         <v>0.000866442097075829</v>
       </c>
-      <c r="J21" s="28">
+      <c r="J21" s="32">
         <v>0.00974532893344695</v>
       </c>
-      <c r="K21" s="29">
+      <c r="K21" s="33">
         <v>0.511020685947625</v>
       </c>
     </row>
@@ -5630,25 +5854,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="27">
         <v>2023</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="28">
         <v>0.670829879340518</v>
       </c>
-      <c r="G22" s="25">
+      <c r="G22" s="29">
         <v>0.000128949065119278</v>
       </c>
-      <c r="H22" s="26">
+      <c r="H22" s="30">
         <v>0.000994749930920144</v>
       </c>
-      <c r="I22" s="27">
+      <c r="I22" s="31">
         <v>0.00138159712627798</v>
       </c>
-      <c r="J22" s="28">
+      <c r="J22" s="32">
         <v>0.0369346965091646</v>
       </c>
-      <c r="K22" s="29">
+      <c r="K22" s="33">
         <v>0.289730128028</v>
       </c>
     </row>
@@ -5671,25 +5895,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="27">
         <v>2023</v>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="28">
         <v>0.154087633951643</v>
       </c>
-      <c r="G23" s="25">
+      <c r="G23" s="29">
         <v>0</v>
       </c>
-      <c r="H23" s="26">
+      <c r="H23" s="30">
         <v>0.0000896926106102087</v>
       </c>
-      <c r="I23" s="27">
+      <c r="I23" s="31">
         <v>0.0000854215339144845</v>
       </c>
-      <c r="J23" s="28">
+      <c r="J23" s="32">
         <v>0.0127406217833454</v>
       </c>
-      <c r="K23" s="29">
+      <c r="K23" s="33">
         <v>0.832996630120487</v>
       </c>
     </row>
@@ -5712,25 +5936,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="27">
         <v>2023</v>
       </c>
-      <c r="F24" s="24">
+      <c r="F24" s="28">
         <v>0.487344917331357</v>
       </c>
-      <c r="G24" s="25">
+      <c r="G24" s="29">
         <v>0.000412711514651259</v>
       </c>
-      <c r="H24" s="26">
+      <c r="H24" s="30">
         <v>0.000176876363421968</v>
       </c>
-      <c r="I24" s="27">
+      <c r="I24" s="31">
         <v>0.000404288830678784</v>
       </c>
-      <c r="J24" s="28">
+      <c r="J24" s="32">
         <v>0.0178982034415087</v>
       </c>
-      <c r="K24" s="29">
+      <c r="K24" s="33">
         <v>0.493763002518383</v>
       </c>
     </row>
@@ -5753,25 +5977,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E25" s="23">
+      <c r="E25" s="27">
         <v>2023</v>
       </c>
-      <c r="F25" s="24">
+      <c r="F25" s="28">
         <v>0.412927573806139</v>
       </c>
-      <c r="G25" s="25">
+      <c r="G25" s="29">
         <v>0.000271807309525801</v>
       </c>
-      <c r="H25" s="26">
+      <c r="H25" s="30">
         <v>0.000365894455130886</v>
       </c>
-      <c r="I25" s="27">
+      <c r="I25" s="31">
         <v>0.000339759136907251</v>
       </c>
-      <c r="J25" s="28">
+      <c r="J25" s="32">
         <v>0.0150173538513005</v>
       </c>
-      <c r="K25" s="29">
+      <c r="K25" s="33">
         <v>0.571077611440997</v>
       </c>
     </row>
@@ -5794,25 +6018,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="27">
         <v>2023</v>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="28">
         <v>0.469863502896596</v>
       </c>
-      <c r="G26" s="25">
+      <c r="G26" s="29">
         <v>0.000589522373507771</v>
       </c>
-      <c r="H26" s="26">
+      <c r="H26" s="30">
         <v>0.000578185404786468</v>
       </c>
-      <c r="I26" s="27">
+      <c r="I26" s="31">
         <v>0.000478986928475064</v>
       </c>
-      <c r="J26" s="28">
+      <c r="J26" s="32">
         <v>0.0219908850771481</v>
       </c>
-      <c r="K26" s="29">
+      <c r="K26" s="33">
         <v>0.506498917319487</v>
       </c>
     </row>
@@ -5835,25 +6059,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="27">
         <v>2024</v>
       </c>
-      <c r="F27" s="24">
+      <c r="F27" s="28">
         <v>0.200656390390875</v>
       </c>
-      <c r="G27" s="25">
+      <c r="G27" s="29">
         <v>0.0000807037365830038</v>
       </c>
-      <c r="H27" s="26">
+      <c r="H27" s="30">
         <v>0.000699432383719366</v>
       </c>
-      <c r="I27" s="27">
+      <c r="I27" s="31">
         <v>0.00156027224060474</v>
       </c>
-      <c r="J27" s="28">
+      <c r="J27" s="32">
         <v>0.0469695746913082</v>
       </c>
-      <c r="K27" s="29">
+      <c r="K27" s="33">
         <v>0.75003362655691</v>
       </c>
     </row>
@@ -5876,25 +6100,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E28" s="23">
+      <c r="E28" s="27">
         <v>2024</v>
       </c>
-      <c r="F28" s="24">
+      <c r="F28" s="28">
         <v>0.0924159578240871</v>
       </c>
-      <c r="G28" s="25">
+      <c r="G28" s="29">
         <v>0.00000264658088215834</v>
       </c>
-      <c r="H28" s="26">
+      <c r="H28" s="30">
         <v>0.0001270358823436</v>
       </c>
-      <c r="I28" s="27">
+      <c r="I28" s="31">
         <v>0.0000396987132323751</v>
       </c>
-      <c r="J28" s="28">
+      <c r="J28" s="32">
         <v>0.0060289112495567</v>
       </c>
-      <c r="K28" s="29">
+      <c r="K28" s="33">
         <v>0.901385749749898</v>
       </c>
     </row>
@@ -5917,25 +6141,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E29" s="23">
+      <c r="E29" s="27">
         <v>2024</v>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="28">
         <v>0.425119194841761</v>
       </c>
-      <c r="G29" s="25">
+      <c r="G29" s="29">
         <v>0.000210000700002333</v>
       </c>
-      <c r="H29" s="26">
+      <c r="H29" s="30">
         <v>0.000233334111113704</v>
       </c>
-      <c r="I29" s="27">
+      <c r="I29" s="31">
         <v>0.000373334577781926</v>
       </c>
-      <c r="J29" s="28">
+      <c r="J29" s="32">
         <v>0.0105544796260432</v>
       </c>
-      <c r="K29" s="29">
+      <c r="K29" s="33">
         <v>0.563509656143298</v>
       </c>
     </row>
@@ -5958,25 +6182,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E30" s="23">
+      <c r="E30" s="27">
         <v>2024</v>
       </c>
-      <c r="F30" s="24">
+      <c r="F30" s="28">
         <v>0.358295795795796</v>
       </c>
-      <c r="G30" s="25">
+      <c r="G30" s="29">
         <v>0.000045777484801875</v>
       </c>
-      <c r="H30" s="26">
+      <c r="H30" s="30">
         <v>0.000251776166410313</v>
       </c>
-      <c r="I30" s="27">
+      <c r="I30" s="31">
         <v>0.000297553651212188</v>
       </c>
-      <c r="J30" s="28">
+      <c r="J30" s="32">
         <v>0.0118289020728045</v>
       </c>
-      <c r="K30" s="29">
+      <c r="K30" s="33">
         <v>0.629280194828975</v>
       </c>
     </row>
@@ -5999,25 +6223,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E31" s="23">
+      <c r="E31" s="27">
         <v>2024</v>
       </c>
-      <c r="F31" s="24">
+      <c r="F31" s="28">
         <v>0.351665344788625</v>
       </c>
-      <c r="G31" s="25">
+      <c r="G31" s="29">
         <v>0.000556074952700397</v>
       </c>
-      <c r="H31" s="26">
+      <c r="H31" s="30">
         <v>0.000436441297537762</v>
       </c>
-      <c r="I31" s="27">
+      <c r="I31" s="31">
         <v>0.000374409031897877</v>
       </c>
-      <c r="J31" s="28">
+      <c r="J31" s="32">
         <v>0.00754578202748029</v>
       </c>
-      <c r="K31" s="29">
+      <c r="K31" s="33">
         <v>0.639421947901759</v>
       </c>
     </row>
@@ -6040,25 +6264,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E32" s="23">
+      <c r="E32" s="27">
         <v>2025</v>
       </c>
-      <c r="F32" s="24">
+      <c r="F32" s="28">
         <v>0.554421768707483</v>
       </c>
-      <c r="G32" s="25">
+      <c r="G32" s="29">
         <v>0.0000459643316786174</v>
       </c>
-      <c r="H32" s="26">
+      <c r="H32" s="30">
         <v>0.000367714653428939</v>
       </c>
-      <c r="I32" s="27">
+      <c r="I32" s="31">
         <v>0</v>
       </c>
-      <c r="J32" s="28">
+      <c r="J32" s="32">
         <v>0.0179873751302323</v>
       </c>
-      <c r="K32" s="29">
+      <c r="K32" s="33">
         <v>0.427177177177177</v>
       </c>
     </row>
@@ -6081,25 +6305,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E33" s="23">
+      <c r="E33" s="27">
         <v>2025</v>
       </c>
-      <c r="F33" s="24">
+      <c r="F33" s="28">
         <v>0.0943438653739554</v>
       </c>
-      <c r="G33" s="25">
+      <c r="G33" s="29">
         <v>0.00000261470720508717</v>
       </c>
-      <c r="H33" s="26">
+      <c r="H33" s="30">
         <v>0.000104588288203487</v>
       </c>
-      <c r="I33" s="27">
+      <c r="I33" s="31">
         <v>0.0000183029504356102</v>
       </c>
-      <c r="J33" s="28">
+      <c r="J33" s="32">
         <v>0.00138840952590129</v>
       </c>
-      <c r="K33" s="29">
+      <c r="K33" s="33">
         <v>0.904142219154299</v>
       </c>
     </row>
@@ -6122,25 +6346,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E34" s="23">
+      <c r="E34" s="27">
         <v>2025</v>
       </c>
-      <c r="F34" s="24">
+      <c r="F34" s="28">
         <v>0.426246770122325</v>
       </c>
-      <c r="G34" s="25">
+      <c r="G34" s="29">
         <v>0.000365928337789195</v>
       </c>
-      <c r="H34" s="26">
+      <c r="H34" s="30">
         <v>0.000201633982047108</v>
       </c>
-      <c r="I34" s="27">
+      <c r="I34" s="31">
         <v>0</v>
       </c>
-      <c r="J34" s="28">
+      <c r="J34" s="32">
         <v>0.00610876286350126</v>
       </c>
-      <c r="K34" s="29">
+      <c r="K34" s="33">
         <v>0.567076904694338</v>
       </c>
     </row>
@@ -6163,25 +6387,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E35" s="23">
+      <c r="E35" s="27">
         <v>2025</v>
       </c>
-      <c r="F35" s="24">
+      <c r="F35" s="28">
         <v>0.370763033337739</v>
       </c>
-      <c r="G35" s="25">
+      <c r="G35" s="29">
         <v>0.0000146840721868989</v>
       </c>
-      <c r="H35" s="26">
+      <c r="H35" s="30">
         <v>0.000220261082803483</v>
       </c>
-      <c r="I35" s="27">
+      <c r="I35" s="31">
         <v>0.00415559242889238</v>
       </c>
-      <c r="J35" s="28">
+      <c r="J35" s="32">
         <v>0.00784618923853296</v>
       </c>
-      <c r="K35" s="29">
+      <c r="K35" s="33">
         <v>0.617000239839846</v>
       </c>
     </row>
@@ -6204,25 +6428,25 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E36" s="23">
+      <c r="E36" s="27">
         <v>2025</v>
       </c>
-      <c r="F36" s="24">
+      <c r="F36" s="28">
         <v>0.318009688592361</v>
       </c>
-      <c r="G36" s="25">
+      <c r="G36" s="29">
         <v>0.000486823833617979</v>
       </c>
-      <c r="H36" s="26">
+      <c r="H36" s="30">
         <v>0.000301272126542274</v>
       </c>
-      <c r="I36" s="27">
+      <c r="I36" s="31">
         <v>0.000117715599112544</v>
       </c>
-      <c r="J36" s="28">
+      <c r="J36" s="32">
         <v>0.00657611211313467</v>
       </c>
-      <c r="K36" s="29">
+      <c r="K36" s="33">
         <v>0.674508387735232</v>
       </c>
     </row>
@@ -6238,35 +6462,35 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="35" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="35" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="35" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="35" t="inlineStr">
         <is>
           <t>Área municipal (km²)</t>
         </is>
@@ -6291,7 +6515,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="30">
+      <c r="E2" s="37">
         <v>296.153167</v>
       </c>
     </row>
@@ -6314,7 +6538,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="30">
+      <c r="E3" s="37">
         <v>203.33231</v>
       </c>
     </row>
@@ -6337,7 +6561,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="37">
         <v>214.195946</v>
       </c>
     </row>
@@ -6360,7 +6584,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="37">
         <v>220.944275</v>
       </c>
     </row>
@@ -6383,32 +6607,32 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="37">
         <v>864.778914</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA DEL RIO GRANDE</t>
-        </is>
-      </c>
-      <c r="E7" s="31">
+      <c r="D7" s="36" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RIO GRANDE</t>
+        </is>
+      </c>
+      <c r="E7" s="38">
         <v>1799.404612</v>
       </c>
     </row>
@@ -6424,41 +6648,41 @@
   <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="29.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="29.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="40" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="40" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="40" t="inlineStr">
         <is>
           <t>Principal cultivo permanente</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="40" t="inlineStr">
         <is>
           <t>Producción total del cultivo permanente (t)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="40" t="inlineStr">
         <is>
           <t>Principal cultivo transitorio</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="40" t="inlineStr">
         <is>
           <t>Producción total del cultivo transitorio (t)</t>
         </is>
@@ -6470,7 +6694,7 @@
           <t>Belmira</t>
         </is>
       </c>
-      <c r="B2" s="32">
+      <c r="B2" s="41">
         <v>2019</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -6478,7 +6702,7 @@
           <t>Aguacate</t>
         </is>
       </c>
-      <c r="D2" s="33">
+      <c r="D2" s="42">
         <v>120</v>
       </c>
       <c r="E2" t="inlineStr">
@@ -6486,7 +6710,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F2" s="34">
+      <c r="F2" s="43">
         <v>9300</v>
       </c>
     </row>
@@ -6496,7 +6720,7 @@
           <t>Donmatías</t>
         </is>
       </c>
-      <c r="B3" s="32">
+      <c r="B3" s="41">
         <v>2019</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -6504,7 +6728,7 @@
           <t>Caña</t>
         </is>
       </c>
-      <c r="D3" s="33">
+      <c r="D3" s="42">
         <v>5530</v>
       </c>
       <c r="E3" t="inlineStr">
@@ -6512,7 +6736,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F3" s="34">
+      <c r="F3" s="43">
         <v>2508.3</v>
       </c>
     </row>
@@ -6522,7 +6746,7 @@
           <t>Entrerríos</t>
         </is>
       </c>
-      <c r="B4" s="32">
+      <c r="B4" s="41">
         <v>2019</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -6530,7 +6754,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="42">
         <v>8060</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -6538,7 +6762,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="43">
         <v>13500</v>
       </c>
     </row>
@@ -6548,7 +6772,7 @@
           <t>San Pedro de los Milagros</t>
         </is>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="41">
         <v>2019</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -6556,7 +6780,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="42">
         <v>3240</v>
       </c>
       <c r="E5" t="inlineStr">
@@ -6564,7 +6788,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="43">
         <v>38663.5</v>
       </c>
     </row>
@@ -6574,7 +6798,7 @@
           <t>Santa Rosa de Osos</t>
         </is>
       </c>
-      <c r="B6" s="32">
+      <c r="B6" s="41">
         <v>2019</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -6582,7 +6806,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="42">
         <v>44222.5</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -6590,7 +6814,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="43">
         <v>28203.4</v>
       </c>
     </row>
@@ -6600,7 +6824,7 @@
           <t>Belmira</t>
         </is>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="41">
         <v>2020</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -6608,7 +6832,7 @@
           <t>Aguacate</t>
         </is>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="42">
         <v>76.8</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -6616,7 +6840,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="43">
         <v>4720</v>
       </c>
     </row>
@@ -6626,7 +6850,7 @@
           <t>Donmatías</t>
         </is>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="41">
         <v>2020</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -6634,7 +6858,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="42">
         <v>4950</v>
       </c>
       <c r="E8" t="inlineStr">
@@ -6642,7 +6866,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="43">
         <v>2508.3</v>
       </c>
     </row>
@@ -6652,7 +6876,7 @@
           <t>Entrerríos</t>
         </is>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="41">
         <v>2020</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -6660,7 +6884,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="42">
         <v>9176</v>
       </c>
       <c r="E9" t="inlineStr">
@@ -6668,7 +6892,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="43">
         <v>17400</v>
       </c>
     </row>
@@ -6678,7 +6902,7 @@
           <t>San Pedro de los Milagros</t>
         </is>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="41">
         <v>2020</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -6686,7 +6910,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="42">
         <v>2880</v>
       </c>
       <c r="E10" t="inlineStr">
@@ -6694,7 +6918,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="43">
         <v>24809</v>
       </c>
     </row>
@@ -6704,7 +6928,7 @@
           <t>Santa Rosa de Osos</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="41">
         <v>2020</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -6712,7 +6936,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="42">
         <v>45647.5</v>
       </c>
       <c r="E11" t="inlineStr">
@@ -6720,7 +6944,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="43">
         <v>27983</v>
       </c>
     </row>
@@ -6730,7 +6954,7 @@
           <t>Belmira</t>
         </is>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="41">
         <v>2021</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -6738,7 +6962,7 @@
           <t>Aguacate</t>
         </is>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="42">
         <v>189.5</v>
       </c>
       <c r="E12" t="inlineStr">
@@ -6746,7 +6970,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="43">
         <v>4760</v>
       </c>
     </row>
@@ -6756,7 +6980,7 @@
           <t>Donmatías</t>
         </is>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="41">
         <v>2021</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -6764,7 +6988,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="42">
         <v>4896.05</v>
       </c>
       <c r="E13" t="inlineStr">
@@ -6772,7 +6996,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="43">
         <v>2460.8</v>
       </c>
     </row>
@@ -6782,7 +7006,7 @@
           <t>Entrerríos</t>
         </is>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="41">
         <v>2021</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -6790,7 +7014,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="42">
         <v>9174.84</v>
       </c>
       <c r="E14" t="inlineStr">
@@ -6798,7 +7022,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="43">
         <v>17900</v>
       </c>
     </row>
@@ -6808,7 +7032,7 @@
           <t>San Pedro de los Milagros</t>
         </is>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="41">
         <v>2021</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -6816,7 +7040,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="42">
         <v>3080</v>
       </c>
       <c r="E15" t="inlineStr">
@@ -6824,7 +7048,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="43">
         <v>26588.5</v>
       </c>
     </row>
@@ -6834,7 +7058,7 @@
           <t>Santa Rosa de Osos</t>
         </is>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="41">
         <v>2021</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -6842,7 +7066,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="42">
         <v>50619</v>
       </c>
       <c r="E16" t="inlineStr">
@@ -6850,7 +7074,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="43">
         <v>31854</v>
       </c>
     </row>
@@ -6860,7 +7084,7 @@
           <t>Belmira</t>
         </is>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="41">
         <v>2022</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -6868,7 +7092,7 @@
           <t>Aguacate</t>
         </is>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="42">
         <v>188.64</v>
       </c>
       <c r="E17" t="inlineStr">
@@ -6876,7 +7100,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="43">
         <v>5300</v>
       </c>
     </row>
@@ -6886,7 +7110,7 @@
           <t>Donmatías</t>
         </is>
       </c>
-      <c r="B18" s="32">
+      <c r="B18" s="41">
         <v>2022</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -6894,7 +7118,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="42">
         <v>7875</v>
       </c>
       <c r="E18" t="inlineStr">
@@ -6902,7 +7126,7 @@
           <t>Tomate</t>
         </is>
       </c>
-      <c r="F18" s="34">
+      <c r="F18" s="43">
         <v>2941</v>
       </c>
     </row>
@@ -6912,7 +7136,7 @@
           <t>Entrerríos</t>
         </is>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="41">
         <v>2022</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -6920,7 +7144,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D19" s="33">
+      <c r="D19" s="42">
         <v>8940</v>
       </c>
       <c r="E19" t="inlineStr">
@@ -6928,7 +7152,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="43">
         <v>27300</v>
       </c>
     </row>
@@ -6938,7 +7162,7 @@
           <t>San Pedro de los Milagros</t>
         </is>
       </c>
-      <c r="B20" s="32">
+      <c r="B20" s="41">
         <v>2022</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -6946,7 +7170,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="42">
         <v>1215</v>
       </c>
       <c r="E20" t="inlineStr">
@@ -6954,7 +7178,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F20" s="34">
+      <c r="F20" s="43">
         <v>26553</v>
       </c>
     </row>
@@ -6964,7 +7188,7 @@
           <t>Santa Rosa de Osos</t>
         </is>
       </c>
-      <c r="B21" s="32">
+      <c r="B21" s="41">
         <v>2022</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -6972,7 +7196,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="42">
         <v>20426</v>
       </c>
       <c r="E21" t="inlineStr">
@@ -6980,7 +7204,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="43">
         <v>22510.2</v>
       </c>
     </row>
@@ -6990,7 +7214,7 @@
           <t>Belmira</t>
         </is>
       </c>
-      <c r="B22" s="32">
+      <c r="B22" s="41">
         <v>2023</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -6998,7 +7222,7 @@
           <t>Fresa</t>
         </is>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="42">
         <v>400</v>
       </c>
       <c r="E22" t="inlineStr">
@@ -7006,7 +7230,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F22" s="34">
+      <c r="F22" s="43">
         <v>11160</v>
       </c>
     </row>
@@ -7016,7 +7240,7 @@
           <t>Donmatías</t>
         </is>
       </c>
-      <c r="B23" s="32">
+      <c r="B23" s="41">
         <v>2023</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -7024,7 +7248,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D23" s="33">
+      <c r="D23" s="42">
         <v>7875</v>
       </c>
       <c r="E23" t="inlineStr">
@@ -7032,7 +7256,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F23" s="34">
+      <c r="F23" s="43">
         <v>2513</v>
       </c>
     </row>
@@ -7042,7 +7266,7 @@
           <t>Entrerríos</t>
         </is>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="41">
         <v>2023</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -7050,7 +7274,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="42">
         <v>9900</v>
       </c>
       <c r="E24" t="inlineStr">
@@ -7058,7 +7282,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F24" s="34">
+      <c r="F24" s="43">
         <v>31200</v>
       </c>
     </row>
@@ -7068,7 +7292,7 @@
           <t>San Pedro de los Milagros</t>
         </is>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="41">
         <v>2023</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -7076,7 +7300,7 @@
           <t>Aguacate</t>
         </is>
       </c>
-      <c r="D25" s="33">
+      <c r="D25" s="42">
         <v>1176</v>
       </c>
       <c r="E25" t="inlineStr">
@@ -7084,7 +7308,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="43">
         <v>29590</v>
       </c>
     </row>
@@ -7094,7 +7318,7 @@
           <t>Santa Rosa de Osos</t>
         </is>
       </c>
-      <c r="B26" s="32">
+      <c r="B26" s="41">
         <v>2023</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -7102,7 +7326,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D26" s="33">
+      <c r="D26" s="42">
         <v>19886</v>
       </c>
       <c r="E26" t="inlineStr">
@@ -7110,7 +7334,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F26" s="34">
+      <c r="F26" s="43">
         <v>17370.5</v>
       </c>
     </row>
@@ -7120,7 +7344,7 @@
           <t>Belmira</t>
         </is>
       </c>
-      <c r="B27" s="32">
+      <c r="B27" s="41">
         <v>2024</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -7128,7 +7352,7 @@
           <t>Aguacate</t>
         </is>
       </c>
-      <c r="D27" s="33">
+      <c r="D27" s="42">
         <v>356.2</v>
       </c>
       <c r="E27" t="inlineStr">
@@ -7136,7 +7360,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="43">
         <v>10550</v>
       </c>
     </row>
@@ -7146,7 +7370,7 @@
           <t>Donmatías</t>
         </is>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="41">
         <v>2024</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -7154,7 +7378,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D28" s="33">
+      <c r="D28" s="42">
         <v>10935</v>
       </c>
       <c r="E28" t="inlineStr">
@@ -7162,7 +7386,7 @@
           <t>Tomate</t>
         </is>
       </c>
-      <c r="F28" s="34">
+      <c r="F28" s="43">
         <v>2898</v>
       </c>
     </row>
@@ -7172,7 +7396,7 @@
           <t>Entrerríos</t>
         </is>
       </c>
-      <c r="B29" s="32">
+      <c r="B29" s="41">
         <v>2024</v>
       </c>
       <c r="C29" t="inlineStr">
@@ -7180,7 +7404,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D29" s="33">
+      <c r="D29" s="42">
         <v>10500</v>
       </c>
       <c r="E29" t="inlineStr">
@@ -7188,7 +7412,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F29" s="34">
+      <c r="F29" s="43">
         <v>28800</v>
       </c>
     </row>
@@ -7198,7 +7422,7 @@
           <t>San Pedro de los Milagros</t>
         </is>
       </c>
-      <c r="B30" s="32">
+      <c r="B30" s="41">
         <v>2024</v>
       </c>
       <c r="C30" t="inlineStr">
@@ -7206,7 +7430,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D30" s="33">
+      <c r="D30" s="42">
         <v>1983.4</v>
       </c>
       <c r="E30" t="inlineStr">
@@ -7214,7 +7438,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F30" s="34">
+      <c r="F30" s="43">
         <v>36915</v>
       </c>
     </row>
@@ -7224,7 +7448,7 @@
           <t>Santa Rosa de Osos</t>
         </is>
       </c>
-      <c r="B31" s="32">
+      <c r="B31" s="41">
         <v>2024</v>
       </c>
       <c r="C31" t="inlineStr">
@@ -7232,7 +7456,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D31" s="33">
+      <c r="D31" s="42">
         <v>23786</v>
       </c>
       <c r="E31" t="inlineStr">
@@ -7240,7 +7464,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F31" s="34">
+      <c r="F31" s="43">
         <v>56956</v>
       </c>
     </row>
@@ -7250,7 +7474,7 @@
           <t>Belmira</t>
         </is>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="41">
         <v>2025</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -7258,7 +7482,7 @@
           <t>Aguacate</t>
         </is>
       </c>
-      <c r="D32" s="33">
+      <c r="D32" s="42">
         <v>364.8</v>
       </c>
       <c r="E32" t="inlineStr">
@@ -7266,7 +7490,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F32" s="34">
+      <c r="F32" s="43">
         <v>9350</v>
       </c>
     </row>
@@ -7276,7 +7500,7 @@
           <t>Donmatías</t>
         </is>
       </c>
-      <c r="B33" s="32">
+      <c r="B33" s="41">
         <v>2025</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -7284,7 +7508,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D33" s="33">
+      <c r="D33" s="42">
         <v>6560</v>
       </c>
       <c r="E33" t="inlineStr">
@@ -7292,7 +7516,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F33" s="34">
+      <c r="F33" s="43">
         <v>1980</v>
       </c>
     </row>
@@ -7302,7 +7526,7 @@
           <t>Entrerríos</t>
         </is>
       </c>
-      <c r="B34" s="32">
+      <c r="B34" s="41">
         <v>2025</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -7310,7 +7534,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D34" s="33">
+      <c r="D34" s="42">
         <v>9900</v>
       </c>
       <c r="E34" t="inlineStr">
@@ -7318,7 +7542,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F34" s="34">
+      <c r="F34" s="43">
         <v>26400</v>
       </c>
     </row>
@@ -7328,7 +7552,7 @@
           <t>San Pedro de los Milagros</t>
         </is>
       </c>
-      <c r="B35" s="32">
+      <c r="B35" s="41">
         <v>2025</v>
       </c>
       <c r="C35" t="inlineStr">
@@ -7336,7 +7560,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D35" s="33">
+      <c r="D35" s="42">
         <v>2209</v>
       </c>
       <c r="E35" t="inlineStr">
@@ -7344,7 +7568,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F35" s="34">
+      <c r="F35" s="43">
         <v>34300</v>
       </c>
     </row>
@@ -7354,7 +7578,7 @@
           <t>Santa Rosa de Osos</t>
         </is>
       </c>
-      <c r="B36" s="32">
+      <c r="B36" s="41">
         <v>2025</v>
       </c>
       <c r="C36" t="inlineStr">
@@ -7362,7 +7586,7 @@
           <t>Tomate de árbol</t>
         </is>
       </c>
-      <c r="D36" s="33">
+      <c r="D36" s="42">
         <v>23786</v>
       </c>
       <c r="E36" t="inlineStr">
@@ -7370,7 +7594,7 @@
           <t>Papa</t>
         </is>
       </c>
-      <c r="F36" s="34">
+      <c r="F36" s="43">
         <v>105156</v>
       </c>
     </row>
@@ -7386,77 +7610,77 @@
   <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="60.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="61.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="45" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="45" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="45" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="45" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="45" t="inlineStr">
         <is>
           <t>Producción de cultivos permanentes (t)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="45" t="inlineStr">
         <is>
           <t>Producción de cultivos transitorios (t)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="45" t="inlineStr">
         <is>
           <t>Producción agrícola total del municipio (t)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="45" t="inlineStr">
         <is>
           <t>Producción agrícola total de la provincia (t)</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="45" t="inlineStr">
         <is>
           <t>Participación del municipio en la producción de la provincia</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="45" t="inlineStr">
         <is>
           <t>Proporción de cultivos permanentes</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="45" t="inlineStr">
         <is>
           <t>Proporción de cultivos transitorios</t>
         </is>
@@ -7481,28 +7705,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="35">
+      <c r="E2" s="47">
         <v>2019</v>
       </c>
-      <c r="F2" s="37">
+      <c r="F2" s="49">
         <v>52599.25</v>
       </c>
-      <c r="G2" s="39">
+      <c r="G2" s="51">
         <v>29089.42</v>
       </c>
-      <c r="H2" s="41">
+      <c r="H2" s="53">
         <v>81688.67</v>
       </c>
-      <c r="I2" s="43">
+      <c r="I2" s="55">
         <v>188550.92</v>
       </c>
-      <c r="J2" s="45">
+      <c r="J2" s="57">
         <v>0.433244611057851</v>
       </c>
-      <c r="K2" s="47">
+      <c r="K2" s="59">
         <v>0.643898964201523</v>
       </c>
-      <c r="L2" s="49">
+      <c r="L2" s="61">
         <v>0.356101035798477</v>
       </c>
     </row>
@@ -7525,28 +7749,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="35">
+      <c r="E3" s="47">
         <v>2019</v>
       </c>
-      <c r="F3" s="37">
+      <c r="F3" s="49">
         <v>4943</v>
       </c>
-      <c r="G3" s="39">
+      <c r="G3" s="51">
         <v>52200.09</v>
       </c>
-      <c r="H3" s="41">
+      <c r="H3" s="53">
         <v>57143.09</v>
       </c>
-      <c r="I3" s="43">
+      <c r="I3" s="55">
         <v>188550.92</v>
       </c>
-      <c r="J3" s="45">
+      <c r="J3" s="57">
         <v>0.303064498438936</v>
       </c>
-      <c r="K3" s="47">
+      <c r="K3" s="59">
         <v>0.0865021475037489</v>
       </c>
-      <c r="L3" s="49">
+      <c r="L3" s="61">
         <v>0.913497852496251</v>
       </c>
     </row>
@@ -7569,28 +7793,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="47">
         <v>2019</v>
       </c>
-      <c r="F4" s="37">
+      <c r="F4" s="49">
         <v>8468.5</v>
       </c>
-      <c r="G4" s="39">
+      <c r="G4" s="51">
         <v>16596.8</v>
       </c>
-      <c r="H4" s="41">
+      <c r="H4" s="53">
         <v>25065.3</v>
       </c>
-      <c r="I4" s="43">
+      <c r="I4" s="55">
         <v>188550.92</v>
       </c>
-      <c r="J4" s="45">
+      <c r="J4" s="57">
         <v>0.132936503306375</v>
       </c>
-      <c r="K4" s="47">
+      <c r="K4" s="59">
         <v>0.33785751616777</v>
       </c>
-      <c r="L4" s="49">
+      <c r="L4" s="61">
         <v>0.66214248383223</v>
       </c>
     </row>
@@ -7613,28 +7837,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="47">
         <v>2019</v>
       </c>
-      <c r="F5" s="37">
+      <c r="F5" s="49">
         <v>10348.76</v>
       </c>
-      <c r="G5" s="39">
+      <c r="G5" s="51">
         <v>4409.6</v>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="53">
         <v>14758.36</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="55">
         <v>188550.92</v>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="57">
         <v>0.0782725430350592</v>
       </c>
-      <c r="K5" s="47">
+      <c r="K5" s="59">
         <v>0.701213413956564</v>
       </c>
-      <c r="L5" s="49">
+      <c r="L5" s="61">
         <v>0.298786586043436</v>
       </c>
     </row>
@@ -7657,74 +7881,74 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="47">
         <v>2019</v>
       </c>
-      <c r="F6" s="37">
+      <c r="F6" s="49">
         <v>132</v>
       </c>
-      <c r="G6" s="39">
+      <c r="G6" s="51">
         <v>9763.5</v>
       </c>
-      <c r="H6" s="41">
+      <c r="H6" s="53">
         <v>9895.5</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="55">
         <v>188550.92</v>
       </c>
-      <c r="J6" s="45">
+      <c r="J6" s="57">
         <v>0.0524818441617787</v>
       </c>
-      <c r="K6" s="47">
+      <c r="K6" s="59">
         <v>0.0133393966954676</v>
       </c>
-      <c r="L6" s="49">
+      <c r="L6" s="61">
         <v>0.986660603304532</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="46" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA DEL RIO GRANDE</t>
-        </is>
-      </c>
-      <c r="E7" s="36">
+      <c r="D7" s="46" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RIO GRANDE</t>
+        </is>
+      </c>
+      <c r="E7" s="48">
         <v>2019</v>
       </c>
-      <c r="F7" s="38">
+      <c r="F7" s="50">
         <v>76491.51</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="52">
         <v>112059.41</v>
       </c>
-      <c r="H7" s="42">
+      <c r="H7" s="54">
         <v>188550.92</v>
       </c>
-      <c r="I7" s="44">
+      <c r="I7" s="56">
         <v>188550.92</v>
       </c>
-      <c r="J7" s="46">
+      <c r="J7" s="58">
         <v>1</v>
       </c>
-      <c r="K7" s="48">
+      <c r="K7" s="60">
         <v>0.405680916327536</v>
       </c>
-      <c r="L7" s="50">
+      <c r="L7" s="62">
         <v>0.594319083672464</v>
       </c>
     </row>
@@ -7747,28 +7971,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="47">
         <v>2020</v>
       </c>
-      <c r="F8" s="37">
+      <c r="F8" s="49">
         <v>54229.75</v>
       </c>
-      <c r="G8" s="39">
+      <c r="G8" s="51">
         <v>28797.16</v>
       </c>
-      <c r="H8" s="41">
+      <c r="H8" s="53">
         <v>83026.91</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="55">
         <v>170615.61</v>
       </c>
-      <c r="J8" s="45">
+      <c r="J8" s="57">
         <v>0.486631381501376</v>
       </c>
-      <c r="K8" s="47">
+      <c r="K8" s="59">
         <v>0.653158716854572</v>
       </c>
-      <c r="L8" s="49">
+      <c r="L8" s="61">
         <v>0.346841283145428</v>
       </c>
     </row>
@@ -7791,28 +8015,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="47">
         <v>2020</v>
       </c>
-      <c r="F9" s="37">
+      <c r="F9" s="49">
         <v>4444</v>
       </c>
-      <c r="G9" s="39">
+      <c r="G9" s="51">
         <v>35224.19</v>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="53">
         <v>39668.19</v>
       </c>
-      <c r="I9" s="43">
+      <c r="I9" s="55">
         <v>170615.61</v>
       </c>
-      <c r="J9" s="45">
+      <c r="J9" s="57">
         <v>0.232500355623967</v>
       </c>
-      <c r="K9" s="47">
+      <c r="K9" s="59">
         <v>0.112029311143261</v>
       </c>
-      <c r="L9" s="49">
+      <c r="L9" s="61">
         <v>0.887970688856739</v>
       </c>
     </row>
@@ -7835,28 +8059,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="47">
         <v>2020</v>
       </c>
-      <c r="F10" s="37">
+      <c r="F10" s="49">
         <v>9604.7</v>
       </c>
-      <c r="G10" s="39">
+      <c r="G10" s="51">
         <v>20493.79</v>
       </c>
-      <c r="H10" s="41">
+      <c r="H10" s="53">
         <v>30098.49</v>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="55">
         <v>170615.61</v>
       </c>
-      <c r="J10" s="45">
+      <c r="J10" s="57">
         <v>0.176411115020484</v>
       </c>
-      <c r="K10" s="47">
+      <c r="K10" s="59">
         <v>0.319109031715545</v>
       </c>
-      <c r="L10" s="49">
+      <c r="L10" s="61">
         <v>0.680890968284456</v>
       </c>
     </row>
@@ -7879,28 +8103,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="47">
         <v>2020</v>
       </c>
-      <c r="F11" s="37">
+      <c r="F11" s="49">
         <v>8647.3</v>
       </c>
-      <c r="G11" s="39">
+      <c r="G11" s="51">
         <v>4130.15</v>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="53">
         <v>12777.45</v>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="55">
         <v>170615.61</v>
       </c>
-      <c r="J11" s="45">
+      <c r="J11" s="57">
         <v>0.0748902752802044</v>
       </c>
-      <c r="K11" s="47">
+      <c r="K11" s="59">
         <v>0.676762577822648</v>
       </c>
-      <c r="L11" s="49">
+      <c r="L11" s="61">
         <v>0.323237422177352</v>
       </c>
     </row>
@@ -7923,74 +8147,74 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E12" s="35">
+      <c r="E12" s="47">
         <v>2020</v>
       </c>
-      <c r="F12" s="37">
+      <c r="F12" s="49">
         <v>94.3</v>
       </c>
-      <c r="G12" s="39">
+      <c r="G12" s="51">
         <v>4950.27</v>
       </c>
-      <c r="H12" s="41">
+      <c r="H12" s="53">
         <v>5044.57</v>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="55">
         <v>170615.61</v>
       </c>
-      <c r="J12" s="45">
+      <c r="J12" s="57">
         <v>0.0295668725739691</v>
       </c>
-      <c r="K12" s="47">
+      <c r="K12" s="59">
         <v>0.0186933673236767</v>
       </c>
-      <c r="L12" s="49">
+      <c r="L12" s="61">
         <v>0.981306632676323</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="46" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA DEL RIO GRANDE</t>
-        </is>
-      </c>
-      <c r="E13" s="36">
+      <c r="D13" s="46" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RIO GRANDE</t>
+        </is>
+      </c>
+      <c r="E13" s="48">
         <v>2020</v>
       </c>
-      <c r="F13" s="38">
+      <c r="F13" s="50">
         <v>77020.05</v>
       </c>
-      <c r="G13" s="40">
+      <c r="G13" s="52">
         <v>93595.56</v>
       </c>
-      <c r="H13" s="42">
+      <c r="H13" s="54">
         <v>170615.61</v>
       </c>
-      <c r="I13" s="44">
+      <c r="I13" s="56">
         <v>170615.61</v>
       </c>
-      <c r="J13" s="46">
+      <c r="J13" s="58">
         <v>1</v>
       </c>
-      <c r="K13" s="48">
+      <c r="K13" s="60">
         <v>0.451424403663885</v>
       </c>
-      <c r="L13" s="50">
+      <c r="L13" s="62">
         <v>0.548575596336115</v>
       </c>
     </row>
@@ -8013,28 +8237,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="47">
         <v>2021</v>
       </c>
-      <c r="F14" s="37">
+      <c r="F14" s="49">
         <v>56830.73</v>
       </c>
-      <c r="G14" s="39">
+      <c r="G14" s="51">
         <v>32323.39</v>
       </c>
-      <c r="H14" s="41">
+      <c r="H14" s="53">
         <v>89154.12</v>
       </c>
-      <c r="I14" s="43">
+      <c r="I14" s="55">
         <v>185514.56</v>
       </c>
-      <c r="J14" s="45">
+      <c r="J14" s="57">
         <v>0.480577481357797</v>
       </c>
-      <c r="K14" s="47">
+      <c r="K14" s="59">
         <v>0.63744367618681</v>
       </c>
-      <c r="L14" s="49">
+      <c r="L14" s="61">
         <v>0.36255632381319</v>
       </c>
     </row>
@@ -8057,28 +8281,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="47">
         <v>2021</v>
       </c>
-      <c r="F15" s="37">
+      <c r="F15" s="49">
         <v>4970.15</v>
       </c>
-      <c r="G15" s="39">
+      <c r="G15" s="51">
         <v>42142.45</v>
       </c>
-      <c r="H15" s="41">
+      <c r="H15" s="53">
         <v>47112.6</v>
       </c>
-      <c r="I15" s="43">
+      <c r="I15" s="55">
         <v>185514.56</v>
       </c>
-      <c r="J15" s="45">
+      <c r="J15" s="57">
         <v>0.253956347146014</v>
       </c>
-      <c r="K15" s="47">
+      <c r="K15" s="59">
         <v>0.105495132936836</v>
       </c>
-      <c r="L15" s="49">
+      <c r="L15" s="61">
         <v>0.894504867063164</v>
       </c>
     </row>
@@ -8101,28 +8325,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="47">
         <v>2021</v>
       </c>
-      <c r="F16" s="37">
+      <c r="F16" s="49">
         <v>10007.38</v>
       </c>
-      <c r="G16" s="39">
+      <c r="G16" s="51">
         <v>21628.29</v>
       </c>
-      <c r="H16" s="41">
+      <c r="H16" s="53">
         <v>31635.67</v>
       </c>
-      <c r="I16" s="43">
+      <c r="I16" s="55">
         <v>185514.56</v>
       </c>
-      <c r="J16" s="45">
+      <c r="J16" s="57">
         <v>0.170529310475685</v>
       </c>
-      <c r="K16" s="47">
+      <c r="K16" s="59">
         <v>0.316332165558687</v>
       </c>
-      <c r="L16" s="49">
+      <c r="L16" s="61">
         <v>0.683667834441313</v>
       </c>
     </row>
@@ -8145,28 +8369,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="47">
         <v>2021</v>
       </c>
-      <c r="F17" s="37">
+      <c r="F17" s="49">
         <v>8479.14</v>
       </c>
-      <c r="G17" s="39">
+      <c r="G17" s="51">
         <v>3649.6</v>
       </c>
-      <c r="H17" s="41">
+      <c r="H17" s="53">
         <v>12128.74</v>
       </c>
-      <c r="I17" s="43">
+      <c r="I17" s="55">
         <v>185514.56</v>
       </c>
-      <c r="J17" s="45">
+      <c r="J17" s="57">
         <v>0.0653789114989142</v>
       </c>
-      <c r="K17" s="47">
+      <c r="K17" s="59">
         <v>0.69909487712656</v>
       </c>
-      <c r="L17" s="49">
+      <c r="L17" s="61">
         <v>0.300905122873439</v>
       </c>
     </row>
@@ -8189,74 +8413,74 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E18" s="35">
+      <c r="E18" s="47">
         <v>2021</v>
       </c>
-      <c r="F18" s="37">
+      <c r="F18" s="49">
         <v>402.92</v>
       </c>
-      <c r="G18" s="39">
+      <c r="G18" s="51">
         <v>5080.51</v>
       </c>
-      <c r="H18" s="41">
+      <c r="H18" s="53">
         <v>5483.43</v>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="55">
         <v>185514.56</v>
       </c>
-      <c r="J18" s="45">
+      <c r="J18" s="57">
         <v>0.0295579495215901</v>
       </c>
-      <c r="K18" s="47">
+      <c r="K18" s="59">
         <v>0.0734795556795655</v>
       </c>
-      <c r="L18" s="49">
+      <c r="L18" s="61">
         <v>0.926520444320434</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="46" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA DEL RIO GRANDE</t>
-        </is>
-      </c>
-      <c r="E19" s="36">
+      <c r="D19" s="46" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RIO GRANDE</t>
+        </is>
+      </c>
+      <c r="E19" s="48">
         <v>2021</v>
       </c>
-      <c r="F19" s="38">
+      <c r="F19" s="50">
         <v>80690.32</v>
       </c>
-      <c r="G19" s="40">
+      <c r="G19" s="52">
         <v>104824.24</v>
       </c>
-      <c r="H19" s="42">
+      <c r="H19" s="54">
         <v>185514.56</v>
       </c>
-      <c r="I19" s="44">
+      <c r="I19" s="56">
         <v>185514.56</v>
       </c>
-      <c r="J19" s="46">
+      <c r="J19" s="58">
         <v>1</v>
       </c>
-      <c r="K19" s="48">
+      <c r="K19" s="60">
         <v>0.434954108184285</v>
       </c>
-      <c r="L19" s="50">
+      <c r="L19" s="62">
         <v>0.565045891815715</v>
       </c>
     </row>
@@ -8279,28 +8503,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E20" s="35">
+      <c r="E20" s="47">
         <v>2022</v>
       </c>
-      <c r="F20" s="37">
+      <c r="F20" s="49">
         <v>26852.96</v>
       </c>
-      <c r="G20" s="39">
+      <c r="G20" s="51">
         <v>22874.53</v>
       </c>
-      <c r="H20" s="41">
+      <c r="H20" s="53">
         <v>49727.49</v>
       </c>
-      <c r="I20" s="43">
+      <c r="I20" s="55">
         <v>157307.7</v>
       </c>
-      <c r="J20" s="45">
+      <c r="J20" s="57">
         <v>0.316116057891635</v>
       </c>
-      <c r="K20" s="47">
+      <c r="K20" s="59">
         <v>0.540002320647996</v>
       </c>
-      <c r="L20" s="49">
+      <c r="L20" s="61">
         <v>0.459997679352004</v>
       </c>
     </row>
@@ -8323,28 +8547,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E21" s="35">
+      <c r="E21" s="47">
         <v>2022</v>
       </c>
-      <c r="F21" s="37">
+      <c r="F21" s="49">
         <v>2422.5</v>
       </c>
-      <c r="G21" s="39">
+      <c r="G21" s="51">
         <v>42088.31</v>
       </c>
-      <c r="H21" s="41">
+      <c r="H21" s="53">
         <v>44510.81</v>
       </c>
-      <c r="I21" s="43">
+      <c r="I21" s="55">
         <v>157307.7</v>
       </c>
-      <c r="J21" s="45">
+      <c r="J21" s="57">
         <v>0.282953790564607</v>
       </c>
-      <c r="K21" s="47">
+      <c r="K21" s="59">
         <v>0.054424981257362</v>
       </c>
-      <c r="L21" s="49">
+      <c r="L21" s="61">
         <v>0.945575018742638</v>
       </c>
     </row>
@@ -8367,28 +8591,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E22" s="35">
+      <c r="E22" s="47">
         <v>2022</v>
       </c>
-      <c r="F22" s="37">
+      <c r="F22" s="49">
         <v>9795</v>
       </c>
-      <c r="G22" s="39">
+      <c r="G22" s="51">
         <v>31411.8</v>
       </c>
-      <c r="H22" s="41">
+      <c r="H22" s="53">
         <v>41206.8</v>
       </c>
-      <c r="I22" s="43">
+      <c r="I22" s="55">
         <v>157307.7</v>
       </c>
-      <c r="J22" s="45">
+      <c r="J22" s="57">
         <v>0.261950305039105</v>
       </c>
-      <c r="K22" s="47">
+      <c r="K22" s="59">
         <v>0.237703485832435</v>
       </c>
-      <c r="L22" s="49">
+      <c r="L22" s="61">
         <v>0.762296514167564</v>
       </c>
     </row>
@@ -8411,28 +8635,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E23" s="35">
+      <c r="E23" s="47">
         <v>2022</v>
       </c>
-      <c r="F23" s="37">
+      <c r="F23" s="49">
         <v>10454.62</v>
       </c>
-      <c r="G23" s="39">
+      <c r="G23" s="51">
         <v>5451.23</v>
       </c>
-      <c r="H23" s="41">
+      <c r="H23" s="53">
         <v>15905.85</v>
       </c>
-      <c r="I23" s="43">
+      <c r="I23" s="55">
         <v>157307.7</v>
       </c>
-      <c r="J23" s="45">
+      <c r="J23" s="57">
         <v>0.101112977940686</v>
       </c>
-      <c r="K23" s="47">
+      <c r="K23" s="59">
         <v>0.657281440476303</v>
       </c>
-      <c r="L23" s="49">
+      <c r="L23" s="61">
         <v>0.342718559523697</v>
       </c>
     </row>
@@ -8455,74 +8679,74 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E24" s="35">
+      <c r="E24" s="47">
         <v>2022</v>
       </c>
-      <c r="F24" s="37">
+      <c r="F24" s="49">
         <v>339.64</v>
       </c>
-      <c r="G24" s="39">
+      <c r="G24" s="51">
         <v>5617.11</v>
       </c>
-      <c r="H24" s="41">
+      <c r="H24" s="53">
         <v>5956.75</v>
       </c>
-      <c r="I24" s="43">
+      <c r="I24" s="55">
         <v>157307.7</v>
       </c>
-      <c r="J24" s="45">
+      <c r="J24" s="57">
         <v>0.0378668685639673</v>
       </c>
-      <c r="K24" s="47">
+      <c r="K24" s="59">
         <v>0.0570176690309313</v>
       </c>
-      <c r="L24" s="49">
+      <c r="L24" s="61">
         <v>0.942982330969069</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="46" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA DEL RIO GRANDE</t>
-        </is>
-      </c>
-      <c r="E25" s="36">
+      <c r="D25" s="46" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RIO GRANDE</t>
+        </is>
+      </c>
+      <c r="E25" s="48">
         <v>2022</v>
       </c>
-      <c r="F25" s="38">
+      <c r="F25" s="50">
         <v>49864.72</v>
       </c>
-      <c r="G25" s="40">
+      <c r="G25" s="52">
         <v>107442.98</v>
       </c>
-      <c r="H25" s="42">
+      <c r="H25" s="54">
         <v>157307.7</v>
       </c>
-      <c r="I25" s="44">
+      <c r="I25" s="56">
         <v>157307.7</v>
       </c>
-      <c r="J25" s="46">
+      <c r="J25" s="58">
         <v>1</v>
       </c>
-      <c r="K25" s="48">
+      <c r="K25" s="60">
         <v>0.316988424597143</v>
       </c>
-      <c r="L25" s="50">
+      <c r="L25" s="62">
         <v>0.683011575402857</v>
       </c>
     </row>
@@ -8545,28 +8769,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E26" s="35">
+      <c r="E26" s="47">
         <v>2023</v>
       </c>
-      <c r="F26" s="37">
+      <c r="F26" s="49">
         <v>2761.98</v>
       </c>
-      <c r="G26" s="39">
+      <c r="G26" s="51">
         <v>48129.17</v>
       </c>
-      <c r="H26" s="41">
+      <c r="H26" s="53">
         <v>50891.15</v>
       </c>
-      <c r="I26" s="43">
+      <c r="I26" s="55">
         <v>173258.5</v>
       </c>
-      <c r="J26" s="45">
+      <c r="J26" s="57">
         <v>0.293729600567938</v>
       </c>
-      <c r="K26" s="47">
+      <c r="K26" s="59">
         <v>0.0542723047130984</v>
       </c>
-      <c r="L26" s="49">
+      <c r="L26" s="61">
         <v>0.945727695286901</v>
       </c>
     </row>
@@ -8589,28 +8813,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E27" s="35">
+      <c r="E27" s="47">
         <v>2023</v>
       </c>
-      <c r="F27" s="37">
+      <c r="F27" s="49">
         <v>29445.24</v>
       </c>
-      <c r="G27" s="39">
+      <c r="G27" s="51">
         <v>17578.67</v>
       </c>
-      <c r="H27" s="41">
+      <c r="H27" s="53">
         <v>47023.91</v>
       </c>
-      <c r="I27" s="43">
+      <c r="I27" s="55">
         <v>173258.5</v>
       </c>
-      <c r="J27" s="45">
+      <c r="J27" s="57">
         <v>0.271408964062369</v>
       </c>
-      <c r="K27" s="47">
+      <c r="K27" s="59">
         <v>0.626175917740571</v>
       </c>
-      <c r="L27" s="49">
+      <c r="L27" s="61">
         <v>0.373824082259429</v>
       </c>
     </row>
@@ -8633,28 +8857,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E28" s="35">
+      <c r="E28" s="47">
         <v>2023</v>
       </c>
-      <c r="F28" s="37">
+      <c r="F28" s="49">
         <v>10647</v>
       </c>
-      <c r="G28" s="39">
+      <c r="G28" s="51">
         <v>35916.5</v>
       </c>
-      <c r="H28" s="41">
+      <c r="H28" s="53">
         <v>46563.5</v>
       </c>
-      <c r="I28" s="43">
+      <c r="I28" s="55">
         <v>173258.5</v>
       </c>
-      <c r="J28" s="45">
+      <c r="J28" s="57">
         <v>0.268751605260348</v>
       </c>
-      <c r="K28" s="47">
+      <c r="K28" s="59">
         <v>0.228655491962589</v>
       </c>
-      <c r="L28" s="49">
+      <c r="L28" s="61">
         <v>0.771344508037411</v>
       </c>
     </row>
@@ -8677,28 +8901,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E29" s="35">
+      <c r="E29" s="47">
         <v>2023</v>
       </c>
-      <c r="F29" s="37">
+      <c r="F29" s="49">
         <v>10882.66</v>
       </c>
-      <c r="G29" s="39">
+      <c r="G29" s="51">
         <v>5422.12</v>
       </c>
-      <c r="H29" s="41">
+      <c r="H29" s="53">
         <v>16304.78</v>
       </c>
-      <c r="I29" s="43">
+      <c r="I29" s="55">
         <v>173258.5</v>
       </c>
-      <c r="J29" s="45">
+      <c r="J29" s="57">
         <v>0.0941066672053608</v>
       </c>
-      <c r="K29" s="47">
+      <c r="K29" s="59">
         <v>0.667452121402435</v>
       </c>
-      <c r="L29" s="49">
+      <c r="L29" s="61">
         <v>0.332547878597565</v>
       </c>
     </row>
@@ -8721,74 +8945,74 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E30" s="35">
+      <c r="E30" s="47">
         <v>2023</v>
       </c>
-      <c r="F30" s="37">
+      <c r="F30" s="49">
         <v>813.7</v>
       </c>
-      <c r="G30" s="39">
+      <c r="G30" s="51">
         <v>11661.46</v>
       </c>
-      <c r="H30" s="41">
+      <c r="H30" s="53">
         <v>12475.16</v>
       </c>
-      <c r="I30" s="43">
+      <c r="I30" s="55">
         <v>173258.5</v>
       </c>
-      <c r="J30" s="45">
+      <c r="J30" s="57">
         <v>0.0720031629039845</v>
       </c>
-      <c r="K30" s="47">
+      <c r="K30" s="59">
         <v>0.0652256163448004</v>
       </c>
-      <c r="L30" s="49">
+      <c r="L30" s="61">
         <v>0.9347743836552</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="46" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA DEL RIO GRANDE</t>
-        </is>
-      </c>
-      <c r="E31" s="36">
+      <c r="D31" s="46" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RIO GRANDE</t>
+        </is>
+      </c>
+      <c r="E31" s="48">
         <v>2023</v>
       </c>
-      <c r="F31" s="38">
+      <c r="F31" s="50">
         <v>54550.58</v>
       </c>
-      <c r="G31" s="40">
+      <c r="G31" s="52">
         <v>118707.92</v>
       </c>
-      <c r="H31" s="42">
+      <c r="H31" s="54">
         <v>173258.5</v>
       </c>
-      <c r="I31" s="44">
+      <c r="I31" s="56">
         <v>173258.5</v>
       </c>
-      <c r="J31" s="46">
+      <c r="J31" s="58">
         <v>1</v>
       </c>
-      <c r="K31" s="48">
+      <c r="K31" s="60">
         <v>0.31485081540011</v>
       </c>
-      <c r="L31" s="50">
+      <c r="L31" s="62">
         <v>0.68514918459989</v>
       </c>
     </row>
@@ -8811,28 +9035,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E32" s="35">
+      <c r="E32" s="47">
         <v>2024</v>
       </c>
-      <c r="F32" s="37">
+      <c r="F32" s="49">
         <v>33867.31</v>
       </c>
-      <c r="G32" s="39">
+      <c r="G32" s="51">
         <v>57128.4</v>
       </c>
-      <c r="H32" s="41">
+      <c r="H32" s="53">
         <v>90995.71</v>
       </c>
-      <c r="I32" s="43">
+      <c r="I32" s="55">
         <v>228931.67</v>
       </c>
-      <c r="J32" s="45">
+      <c r="J32" s="57">
         <v>0.397479780757289</v>
       </c>
-      <c r="K32" s="47">
+      <c r="K32" s="59">
         <v>0.37218578765966</v>
       </c>
-      <c r="L32" s="49">
+      <c r="L32" s="61">
         <v>0.62781421234034</v>
       </c>
     </row>
@@ -8855,28 +9079,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E33" s="35">
+      <c r="E33" s="47">
         <v>2024</v>
       </c>
-      <c r="F33" s="37">
+      <c r="F33" s="49">
         <v>3581.18</v>
       </c>
-      <c r="G33" s="39">
+      <c r="G33" s="51">
         <v>54628.64</v>
       </c>
-      <c r="H33" s="41">
+      <c r="H33" s="53">
         <v>58209.82</v>
       </c>
-      <c r="I33" s="43">
+      <c r="I33" s="55">
         <v>228931.67</v>
       </c>
-      <c r="J33" s="45">
+      <c r="J33" s="57">
         <v>0.254267223053936</v>
       </c>
-      <c r="K33" s="47">
+      <c r="K33" s="59">
         <v>0.0615219219025244</v>
       </c>
-      <c r="L33" s="49">
+      <c r="L33" s="61">
         <v>0.938478078097476</v>
       </c>
     </row>
@@ -8899,28 +9123,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E34" s="35">
+      <c r="E34" s="47">
         <v>2024</v>
       </c>
-      <c r="F34" s="37">
+      <c r="F34" s="49">
         <v>11806.6</v>
       </c>
-      <c r="G34" s="39">
+      <c r="G34" s="51">
         <v>34087</v>
       </c>
-      <c r="H34" s="41">
+      <c r="H34" s="53">
         <v>45893.6</v>
       </c>
-      <c r="I34" s="43">
+      <c r="I34" s="55">
         <v>228931.67</v>
       </c>
-      <c r="J34" s="45">
+      <c r="J34" s="57">
         <v>0.20046855028839</v>
       </c>
-      <c r="K34" s="47">
+      <c r="K34" s="59">
         <v>0.257260271584709</v>
       </c>
-      <c r="L34" s="49">
+      <c r="L34" s="61">
         <v>0.742739728415291</v>
       </c>
     </row>
@@ -8943,28 +9167,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E35" s="35">
+      <c r="E35" s="47">
         <v>2024</v>
       </c>
-      <c r="F35" s="37">
+      <c r="F35" s="49">
         <v>15893.54</v>
       </c>
-      <c r="G35" s="39">
+      <c r="G35" s="51">
         <v>6062.01</v>
       </c>
-      <c r="H35" s="41">
+      <c r="H35" s="53">
         <v>21955.55</v>
       </c>
-      <c r="I35" s="43">
+      <c r="I35" s="55">
         <v>228931.67</v>
       </c>
-      <c r="J35" s="45">
+      <c r="J35" s="57">
         <v>0.0959043805516292</v>
       </c>
-      <c r="K35" s="47">
+      <c r="K35" s="59">
         <v>0.723896235803703</v>
       </c>
-      <c r="L35" s="49">
+      <c r="L35" s="61">
         <v>0.276103764196297</v>
       </c>
     </row>
@@ -8987,74 +9211,74 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E36" s="35">
+      <c r="E36" s="47">
         <v>2024</v>
       </c>
-      <c r="F36" s="37">
+      <c r="F36" s="49">
         <v>731.7</v>
       </c>
-      <c r="G36" s="39">
+      <c r="G36" s="51">
         <v>11145.29</v>
       </c>
-      <c r="H36" s="41">
+      <c r="H36" s="53">
         <v>11876.99</v>
       </c>
-      <c r="I36" s="43">
+      <c r="I36" s="55">
         <v>228931.67</v>
       </c>
-      <c r="J36" s="45">
+      <c r="J36" s="57">
         <v>0.0518800653487567</v>
       </c>
-      <c r="K36" s="47">
+      <c r="K36" s="59">
         <v>0.0616065181498006</v>
       </c>
-      <c r="L36" s="49">
+      <c r="L36" s="61">
         <v>0.938393481850199</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="46" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA DEL RIO GRANDE</t>
-        </is>
-      </c>
-      <c r="E37" s="36">
+      <c r="D37" s="46" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RIO GRANDE</t>
+        </is>
+      </c>
+      <c r="E37" s="48">
         <v>2024</v>
       </c>
-      <c r="F37" s="38">
+      <c r="F37" s="50">
         <v>65880.33</v>
       </c>
-      <c r="G37" s="40">
+      <c r="G37" s="52">
         <v>163051.34</v>
       </c>
-      <c r="H37" s="42">
+      <c r="H37" s="54">
         <v>228931.67</v>
       </c>
-      <c r="I37" s="44">
+      <c r="I37" s="56">
         <v>228931.67</v>
       </c>
-      <c r="J37" s="46">
+      <c r="J37" s="58">
         <v>1</v>
       </c>
-      <c r="K37" s="48">
+      <c r="K37" s="60">
         <v>0.287772897476352</v>
       </c>
-      <c r="L37" s="50">
+      <c r="L37" s="62">
         <v>0.712227102523648</v>
       </c>
     </row>
@@ -9077,28 +9301,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E38" s="35">
+      <c r="E38" s="47">
         <v>2025</v>
       </c>
-      <c r="F38" s="37">
+      <c r="F38" s="49">
         <v>28465.68</v>
       </c>
-      <c r="G38" s="39">
+      <c r="G38" s="51">
         <v>105296.26</v>
       </c>
-      <c r="H38" s="41">
+      <c r="H38" s="53">
         <v>133761.94</v>
       </c>
-      <c r="I38" s="43">
+      <c r="I38" s="55">
         <v>249792.76</v>
       </c>
-      <c r="J38" s="45">
+      <c r="J38" s="57">
         <v>0.535491661167441</v>
       </c>
-      <c r="K38" s="47">
+      <c r="K38" s="59">
         <v>0.212808516383659</v>
       </c>
-      <c r="L38" s="49">
+      <c r="L38" s="61">
         <v>0.787191483616341</v>
       </c>
     </row>
@@ -9121,28 +9345,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E39" s="35">
+      <c r="E39" s="47">
         <v>2025</v>
       </c>
-      <c r="F39" s="37">
+      <c r="F39" s="49">
         <v>3847.38</v>
       </c>
-      <c r="G39" s="39">
+      <c r="G39" s="51">
         <v>42892.14</v>
       </c>
-      <c r="H39" s="41">
+      <c r="H39" s="53">
         <v>46739.52</v>
       </c>
-      <c r="I39" s="43">
+      <c r="I39" s="55">
         <v>249792.76</v>
       </c>
-      <c r="J39" s="45">
+      <c r="J39" s="57">
         <v>0.187113189349443</v>
       </c>
-      <c r="K39" s="47">
+      <c r="K39" s="59">
         <v>0.0823153511204223</v>
       </c>
-      <c r="L39" s="49">
+      <c r="L39" s="61">
         <v>0.917684648879578</v>
       </c>
     </row>
@@ -9165,28 +9389,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E40" s="35">
+      <c r="E40" s="47">
         <v>2025</v>
       </c>
-      <c r="F40" s="37">
+      <c r="F40" s="49">
         <v>11326.4</v>
       </c>
-      <c r="G40" s="39">
+      <c r="G40" s="51">
         <v>31557.28</v>
       </c>
-      <c r="H40" s="41">
+      <c r="H40" s="53">
         <v>42883.68</v>
       </c>
-      <c r="I40" s="43">
+      <c r="I40" s="55">
         <v>249792.76</v>
       </c>
-      <c r="J40" s="45">
+      <c r="J40" s="57">
         <v>0.171677033393602</v>
       </c>
-      <c r="K40" s="47">
+      <c r="K40" s="59">
         <v>0.264119124105021</v>
       </c>
-      <c r="L40" s="49">
+      <c r="L40" s="61">
         <v>0.735880875894979</v>
       </c>
     </row>
@@ -9209,28 +9433,28 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E41" s="35">
+      <c r="E41" s="47">
         <v>2025</v>
       </c>
-      <c r="F41" s="37">
+      <c r="F41" s="49">
         <v>11298.03</v>
       </c>
-      <c r="G41" s="39">
+      <c r="G41" s="51">
         <v>4596.98</v>
       </c>
-      <c r="H41" s="41">
+      <c r="H41" s="53">
         <v>15895.01</v>
       </c>
-      <c r="I41" s="43">
+      <c r="I41" s="55">
         <v>249792.76</v>
       </c>
-      <c r="J41" s="45">
+      <c r="J41" s="57">
         <v>0.0636327890367999</v>
       </c>
-      <c r="K41" s="47">
+      <c r="K41" s="59">
         <v>0.710790996671282</v>
       </c>
-      <c r="L41" s="49">
+      <c r="L41" s="61">
         <v>0.289209003328718</v>
       </c>
     </row>
@@ -9253,74 +9477,74 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E42" s="35">
+      <c r="E42" s="47">
         <v>2025</v>
       </c>
-      <c r="F42" s="37">
+      <c r="F42" s="49">
         <v>593.8</v>
       </c>
-      <c r="G42" s="39">
+      <c r="G42" s="51">
         <v>9918.81</v>
       </c>
-      <c r="H42" s="41">
+      <c r="H42" s="53">
         <v>10512.61</v>
       </c>
-      <c r="I42" s="43">
+      <c r="I42" s="55">
         <v>249792.76</v>
       </c>
-      <c r="J42" s="45">
+      <c r="J42" s="57">
         <v>0.0420853270527136</v>
       </c>
-      <c r="K42" s="47">
+      <c r="K42" s="59">
         <v>0.0564845457027322</v>
       </c>
-      <c r="L42" s="49">
+      <c r="L42" s="61">
         <v>0.943515454297268</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="46" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="46" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA DEL RIO GRANDE</t>
-        </is>
-      </c>
-      <c r="E43" s="36">
+      <c r="D43" s="46" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RIO GRANDE</t>
+        </is>
+      </c>
+      <c r="E43" s="48">
         <v>2025</v>
       </c>
-      <c r="F43" s="38">
+      <c r="F43" s="50">
         <v>55531.29</v>
       </c>
-      <c r="G43" s="40">
+      <c r="G43" s="52">
         <v>194261.47</v>
       </c>
-      <c r="H43" s="42">
+      <c r="H43" s="54">
         <v>249792.76</v>
       </c>
-      <c r="I43" s="44">
+      <c r="I43" s="56">
         <v>249792.76</v>
       </c>
-      <c r="J43" s="46">
+      <c r="J43" s="58">
         <v>1</v>
       </c>
-      <c r="K43" s="48">
+      <c r="K43" s="60">
         <v>0.222309445638056</v>
       </c>
-      <c r="L43" s="50">
+      <c r="L43" s="62">
         <v>0.777690554361944</v>
       </c>
     </row>
@@ -9336,53 +9560,53 @@
   <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="64" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="64" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="64" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="64" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="64" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="64" t="inlineStr">
         <is>
           <t>Producción total (t)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="64" t="inlineStr">
         <is>
           <t>Área cosechada total (ha)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="64" t="inlineStr">
         <is>
           <t>Rendimiento (t/ha)</t>
         </is>
@@ -9407,16 +9631,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="51">
+      <c r="E2" s="66">
         <v>2019</v>
       </c>
-      <c r="F2" s="53">
+      <c r="F2" s="68">
         <v>25065.3</v>
       </c>
-      <c r="G2" s="55">
+      <c r="G2" s="70">
         <v>843</v>
       </c>
-      <c r="H2" s="57">
+      <c r="H2" s="72">
         <v>29.7334519572954</v>
       </c>
     </row>
@@ -9439,16 +9663,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="51">
+      <c r="E3" s="66">
         <v>2019</v>
       </c>
-      <c r="F3" s="53">
+      <c r="F3" s="68">
         <v>57143.09</v>
       </c>
-      <c r="G3" s="55">
+      <c r="G3" s="70">
         <v>2067.4</v>
       </c>
-      <c r="H3" s="57">
+      <c r="H3" s="72">
         <v>27.6400744896972</v>
       </c>
     </row>
@@ -9471,16 +9695,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="51">
+      <c r="E4" s="66">
         <v>2019</v>
       </c>
-      <c r="F4" s="53">
+      <c r="F4" s="68">
         <v>81688.67</v>
       </c>
-      <c r="G4" s="55">
+      <c r="G4" s="70">
         <v>3218.8</v>
       </c>
-      <c r="H4" s="57">
+      <c r="H4" s="72">
         <v>25.3786100410091</v>
       </c>
     </row>
@@ -9503,16 +9727,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="51">
+      <c r="E5" s="66">
         <v>2019</v>
       </c>
-      <c r="F5" s="53">
+      <c r="F5" s="68">
         <v>14758.36</v>
       </c>
-      <c r="G5" s="55">
+      <c r="G5" s="70">
         <v>673.5</v>
       </c>
-      <c r="H5" s="57">
+      <c r="H5" s="72">
         <v>21.9129324424647</v>
       </c>
     </row>
@@ -9535,50 +9759,50 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="51">
+      <c r="E6" s="66">
         <v>2019</v>
       </c>
-      <c r="F6" s="53">
+      <c r="F6" s="68">
         <v>9895.5</v>
       </c>
-      <c r="G6" s="55">
+      <c r="G6" s="70">
         <v>932</v>
       </c>
-      <c r="H6" s="57">
+      <c r="H6" s="72">
         <v>10.6174892703863</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="65" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA DEL RIO GRANDE</t>
-        </is>
-      </c>
-      <c r="E7" s="52">
+      <c r="D7" s="65" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RIO GRANDE</t>
+        </is>
+      </c>
+      <c r="E7" s="67">
         <v>2019</v>
       </c>
-      <c r="F7" s="54">
+      <c r="F7" s="69">
         <v>188550.92</v>
       </c>
-      <c r="G7" s="56">
+      <c r="G7" s="71">
         <v>7734.7</v>
       </c>
-      <c r="H7" s="58">
+      <c r="H7" s="73">
         <v>24.3772764295965</v>
       </c>
     </row>
@@ -9601,16 +9825,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="66">
         <v>2020</v>
       </c>
-      <c r="F8" s="53">
+      <c r="F8" s="68">
         <v>30098.49</v>
       </c>
-      <c r="G8" s="55">
+      <c r="G8" s="70">
         <v>1019</v>
       </c>
-      <c r="H8" s="57">
+      <c r="H8" s="72">
         <v>29.5372816486752</v>
       </c>
     </row>
@@ -9633,16 +9857,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E9" s="51">
+      <c r="E9" s="66">
         <v>2020</v>
       </c>
-      <c r="F9" s="53">
+      <c r="F9" s="68">
         <v>39668.19</v>
       </c>
-      <c r="G9" s="55">
+      <c r="G9" s="70">
         <v>1466</v>
       </c>
-      <c r="H9" s="57">
+      <c r="H9" s="72">
         <v>27.058792633015</v>
       </c>
     </row>
@@ -9665,16 +9889,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="66">
         <v>2020</v>
       </c>
-      <c r="F10" s="53">
+      <c r="F10" s="68">
         <v>83026.91</v>
       </c>
-      <c r="G10" s="55">
+      <c r="G10" s="70">
         <v>3304.5</v>
       </c>
-      <c r="H10" s="57">
+      <c r="H10" s="72">
         <v>25.1254077772734</v>
       </c>
     </row>
@@ -9697,16 +9921,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E11" s="51">
+      <c r="E11" s="66">
         <v>2020</v>
       </c>
-      <c r="F11" s="53">
+      <c r="F11" s="68">
         <v>12777.45</v>
       </c>
-      <c r="G11" s="55">
+      <c r="G11" s="70">
         <v>596</v>
       </c>
-      <c r="H11" s="57">
+      <c r="H11" s="72">
         <v>21.4386744966443</v>
       </c>
     </row>
@@ -9729,50 +9953,50 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E12" s="51">
+      <c r="E12" s="66">
         <v>2020</v>
       </c>
-      <c r="F12" s="53">
+      <c r="F12" s="68">
         <v>5044.57</v>
       </c>
-      <c r="G12" s="55">
+      <c r="G12" s="70">
         <v>487.9</v>
       </c>
-      <c r="H12" s="57">
+      <c r="H12" s="72">
         <v>10.3393523262964</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="65" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA DEL RIO GRANDE</t>
-        </is>
-      </c>
-      <c r="E13" s="52">
+      <c r="D13" s="65" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RIO GRANDE</t>
+        </is>
+      </c>
+      <c r="E13" s="67">
         <v>2020</v>
       </c>
-      <c r="F13" s="54">
+      <c r="F13" s="69">
         <v>170615.61</v>
       </c>
-      <c r="G13" s="56">
+      <c r="G13" s="71">
         <v>6873.4</v>
       </c>
-      <c r="H13" s="58">
+      <c r="H13" s="73">
         <v>24.8225928943463</v>
       </c>
     </row>
@@ -9795,16 +10019,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="66">
         <v>2021</v>
       </c>
-      <c r="F14" s="53">
+      <c r="F14" s="68">
         <v>47112.6</v>
       </c>
-      <c r="G14" s="55">
+      <c r="G14" s="70">
         <v>1658.7</v>
       </c>
-      <c r="H14" s="57">
+      <c r="H14" s="72">
         <v>28.4033279073974</v>
       </c>
     </row>
@@ -9827,16 +10051,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E15" s="51">
+      <c r="E15" s="66">
         <v>2021</v>
       </c>
-      <c r="F15" s="53">
+      <c r="F15" s="68">
         <v>31635.67</v>
       </c>
-      <c r="G15" s="55">
+      <c r="G15" s="70">
         <v>1138.85</v>
       </c>
-      <c r="H15" s="57">
+      <c r="H15" s="72">
         <v>27.7786100013171</v>
       </c>
     </row>
@@ -9859,16 +10083,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E16" s="51">
+      <c r="E16" s="66">
         <v>2021</v>
       </c>
-      <c r="F16" s="53">
+      <c r="F16" s="68">
         <v>89154.12</v>
       </c>
-      <c r="G16" s="55">
+      <c r="G16" s="70">
         <v>3493.06</v>
       </c>
-      <c r="H16" s="57">
+      <c r="H16" s="72">
         <v>25.5232146026693</v>
       </c>
     </row>
@@ -9891,16 +10115,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="66">
         <v>2021</v>
       </c>
-      <c r="F17" s="53">
+      <c r="F17" s="68">
         <v>12128.74</v>
       </c>
-      <c r="G17" s="55">
+      <c r="G17" s="70">
         <v>614.08</v>
       </c>
-      <c r="H17" s="57">
+      <c r="H17" s="72">
         <v>19.7510747785305</v>
       </c>
     </row>
@@ -9923,50 +10147,50 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E18" s="51">
+      <c r="E18" s="66">
         <v>2021</v>
       </c>
-      <c r="F18" s="53">
+      <c r="F18" s="68">
         <v>5483.43</v>
       </c>
-      <c r="G18" s="55">
+      <c r="G18" s="70">
         <v>545.9</v>
       </c>
-      <c r="H18" s="57">
+      <c r="H18" s="72">
         <v>10.0447517860414</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="65" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA DEL RIO GRANDE</t>
-        </is>
-      </c>
-      <c r="E19" s="52">
+      <c r="D19" s="65" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RIO GRANDE</t>
+        </is>
+      </c>
+      <c r="E19" s="67">
         <v>2021</v>
       </c>
-      <c r="F19" s="54">
+      <c r="F19" s="69">
         <v>185514.56</v>
       </c>
-      <c r="G19" s="56">
+      <c r="G19" s="71">
         <v>7450.59</v>
       </c>
-      <c r="H19" s="58">
+      <c r="H19" s="73">
         <v>24.8993113297068</v>
       </c>
     </row>
@@ -9989,16 +10213,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="66">
         <v>2022</v>
       </c>
-      <c r="F20" s="53">
+      <c r="F20" s="68">
         <v>44510.81</v>
       </c>
-      <c r="G20" s="55">
+      <c r="G20" s="70">
         <v>1517.5</v>
       </c>
-      <c r="H20" s="57">
+      <c r="H20" s="72">
         <v>29.3316705107084</v>
       </c>
     </row>
@@ -10021,16 +10245,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E21" s="51">
+      <c r="E21" s="66">
         <v>2022</v>
       </c>
-      <c r="F21" s="53">
+      <c r="F21" s="68">
         <v>41206.8</v>
       </c>
-      <c r="G21" s="55">
+      <c r="G21" s="70">
         <v>1414</v>
       </c>
-      <c r="H21" s="57">
+      <c r="H21" s="72">
         <v>29.1420084865629</v>
       </c>
     </row>
@@ -10053,16 +10277,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E22" s="51">
+      <c r="E22" s="66">
         <v>2022</v>
       </c>
-      <c r="F22" s="53">
+      <c r="F22" s="68">
         <v>15905.85</v>
       </c>
-      <c r="G22" s="55">
+      <c r="G22" s="70">
         <v>559.26</v>
       </c>
-      <c r="H22" s="57">
+      <c r="H22" s="72">
         <v>28.4408861710117</v>
       </c>
     </row>
@@ -10085,16 +10309,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E23" s="51">
+      <c r="E23" s="66">
         <v>2022</v>
       </c>
-      <c r="F23" s="53">
+      <c r="F23" s="68">
         <v>49727.49</v>
       </c>
-      <c r="G23" s="55">
+      <c r="G23" s="70">
         <v>2771.54</v>
       </c>
-      <c r="H23" s="57">
+      <c r="H23" s="72">
         <v>17.9421873759715</v>
       </c>
     </row>
@@ -10117,50 +10341,50 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E24" s="51">
+      <c r="E24" s="66">
         <v>2022</v>
       </c>
-      <c r="F24" s="53">
+      <c r="F24" s="68">
         <v>5956.75</v>
       </c>
-      <c r="G24" s="55">
+      <c r="G24" s="70">
         <v>565.9</v>
       </c>
-      <c r="H24" s="57">
+      <c r="H24" s="72">
         <v>10.5261530305708</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="65" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA DEL RIO GRANDE</t>
-        </is>
-      </c>
-      <c r="E25" s="52">
+      <c r="D25" s="65" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RIO GRANDE</t>
+        </is>
+      </c>
+      <c r="E25" s="67">
         <v>2022</v>
       </c>
-      <c r="F25" s="54">
+      <c r="F25" s="69">
         <v>157307.7</v>
       </c>
-      <c r="G25" s="56">
+      <c r="G25" s="71">
         <v>6828.2</v>
       </c>
-      <c r="H25" s="58">
+      <c r="H25" s="73">
         <v>23.0379455786298</v>
       </c>
     </row>
@@ -10183,16 +10407,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E26" s="51">
+      <c r="E26" s="66">
         <v>2023</v>
       </c>
-      <c r="F26" s="53">
+      <c r="F26" s="68">
         <v>50891.15</v>
       </c>
-      <c r="G26" s="55">
+      <c r="G26" s="70">
         <v>1544.3</v>
       </c>
-      <c r="H26" s="57">
+      <c r="H26" s="72">
         <v>32.9541863627534</v>
       </c>
     </row>
@@ -10215,16 +10439,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E27" s="51">
+      <c r="E27" s="66">
         <v>2023</v>
       </c>
-      <c r="F27" s="53">
+      <c r="F27" s="68">
         <v>46563.5</v>
       </c>
-      <c r="G27" s="55">
+      <c r="G27" s="70">
         <v>1608.5</v>
       </c>
-      <c r="H27" s="57">
+      <c r="H27" s="72">
         <v>28.9483991296239</v>
       </c>
     </row>
@@ -10247,16 +10471,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E28" s="51">
+      <c r="E28" s="66">
         <v>2023</v>
       </c>
-      <c r="F28" s="53">
+      <c r="F28" s="68">
         <v>16304.78</v>
       </c>
-      <c r="G28" s="55">
+      <c r="G28" s="70">
         <v>580.11</v>
       </c>
-      <c r="H28" s="57">
+      <c r="H28" s="72">
         <v>28.106359138784</v>
       </c>
     </row>
@@ -10279,16 +10503,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E29" s="51">
+      <c r="E29" s="66">
         <v>2023</v>
       </c>
-      <c r="F29" s="53">
+      <c r="F29" s="68">
         <v>47023.91</v>
       </c>
-      <c r="G29" s="55">
+      <c r="G29" s="70">
         <v>2455.95</v>
       </c>
-      <c r="H29" s="57">
+      <c r="H29" s="72">
         <v>19.1469329587329</v>
       </c>
     </row>
@@ -10311,50 +10535,50 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E30" s="51">
+      <c r="E30" s="66">
         <v>2023</v>
       </c>
-      <c r="F30" s="53">
+      <c r="F30" s="68">
         <v>12475.16</v>
       </c>
-      <c r="G30" s="55">
+      <c r="G30" s="70">
         <v>1062.9</v>
       </c>
-      <c r="H30" s="57">
+      <c r="H30" s="72">
         <v>11.7369084579923</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="65" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA DEL RIO GRANDE</t>
-        </is>
-      </c>
-      <c r="E31" s="52">
+      <c r="D31" s="65" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RIO GRANDE</t>
+        </is>
+      </c>
+      <c r="E31" s="67">
         <v>2023</v>
       </c>
-      <c r="F31" s="54">
+      <c r="F31" s="69">
         <v>173258.5</v>
       </c>
-      <c r="G31" s="56">
+      <c r="G31" s="71">
         <v>7251.76</v>
       </c>
-      <c r="H31" s="58">
+      <c r="H31" s="73">
         <v>23.8919241673745</v>
       </c>
     </row>
@@ -10377,16 +10601,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E32" s="51">
+      <c r="E32" s="66">
         <v>2024</v>
       </c>
-      <c r="F32" s="53">
+      <c r="F32" s="68">
         <v>58209.82</v>
       </c>
-      <c r="G32" s="55">
+      <c r="G32" s="70">
         <v>1743.49</v>
       </c>
-      <c r="H32" s="57">
+      <c r="H32" s="72">
         <v>33.386953753678</v>
       </c>
     </row>
@@ -10409,16 +10633,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E33" s="51">
+      <c r="E33" s="66">
         <v>2024</v>
       </c>
-      <c r="F33" s="53">
+      <c r="F33" s="68">
         <v>21955.55</v>
       </c>
-      <c r="G33" s="55">
+      <c r="G33" s="70">
         <v>770.56</v>
       </c>
-      <c r="H33" s="57">
+      <c r="H33" s="72">
         <v>28.4929791320598</v>
       </c>
     </row>
@@ -10441,16 +10665,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E34" s="51">
+      <c r="E34" s="66">
         <v>2024</v>
       </c>
-      <c r="F34" s="53">
+      <c r="F34" s="68">
         <v>45893.6</v>
       </c>
-      <c r="G34" s="55">
+      <c r="G34" s="70">
         <v>1627</v>
       </c>
-      <c r="H34" s="57">
+      <c r="H34" s="72">
         <v>28.2074984634296</v>
       </c>
     </row>
@@ -10473,16 +10697,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E35" s="51">
+      <c r="E35" s="66">
         <v>2024</v>
       </c>
-      <c r="F35" s="53">
+      <c r="F35" s="68">
         <v>90995.71</v>
       </c>
-      <c r="G35" s="55">
+      <c r="G35" s="70">
         <v>3240.62</v>
       </c>
-      <c r="H35" s="57">
+      <c r="H35" s="72">
         <v>28.0797223988002</v>
       </c>
     </row>
@@ -10505,50 +10729,50 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E36" s="51">
+      <c r="E36" s="66">
         <v>2024</v>
       </c>
-      <c r="F36" s="53">
+      <c r="F36" s="68">
         <v>11876.99</v>
       </c>
-      <c r="G36" s="55">
+      <c r="G36" s="70">
         <v>1209.9</v>
       </c>
-      <c r="H36" s="57">
+      <c r="H36" s="72">
         <v>9.81650549632201</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="65" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA DEL RIO GRANDE</t>
-        </is>
-      </c>
-      <c r="E37" s="52">
+      <c r="D37" s="65" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RIO GRANDE</t>
+        </is>
+      </c>
+      <c r="E37" s="67">
         <v>2024</v>
       </c>
-      <c r="F37" s="54">
+      <c r="F37" s="69">
         <v>228931.67</v>
       </c>
-      <c r="G37" s="56">
+      <c r="G37" s="71">
         <v>8591.57</v>
       </c>
-      <c r="H37" s="58">
+      <c r="H37" s="73">
         <v>26.6460809840344</v>
       </c>
     </row>
@@ -10571,16 +10795,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E38" s="51">
+      <c r="E38" s="66">
         <v>2025</v>
       </c>
-      <c r="F38" s="53">
+      <c r="F38" s="68">
         <v>133761.94</v>
       </c>
-      <c r="G38" s="55">
+      <c r="G38" s="70">
         <v>4071.52</v>
       </c>
-      <c r="H38" s="57">
+      <c r="H38" s="72">
         <v>32.853072071364</v>
       </c>
     </row>
@@ -10603,16 +10827,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E39" s="51">
+      <c r="E39" s="66">
         <v>2025</v>
       </c>
-      <c r="F39" s="53">
+      <c r="F39" s="68">
         <v>42883.68</v>
       </c>
-      <c r="G39" s="55">
+      <c r="G39" s="70">
         <v>1542</v>
       </c>
-      <c r="H39" s="57">
+      <c r="H39" s="72">
         <v>27.8104280155642</v>
       </c>
     </row>
@@ -10635,16 +10859,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E40" s="51">
+      <c r="E40" s="66">
         <v>2025</v>
       </c>
-      <c r="F40" s="53">
+      <c r="F40" s="68">
         <v>46739.52</v>
       </c>
-      <c r="G40" s="55">
+      <c r="G40" s="70">
         <v>1716</v>
       </c>
-      <c r="H40" s="57">
+      <c r="H40" s="72">
         <v>27.2374825174825</v>
       </c>
     </row>
@@ -10667,16 +10891,16 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E41" s="51">
+      <c r="E41" s="66">
         <v>2025</v>
       </c>
-      <c r="F41" s="53">
+      <c r="F41" s="68">
         <v>15895.01</v>
       </c>
-      <c r="G41" s="55">
+      <c r="G41" s="70">
         <v>730.99</v>
       </c>
-      <c r="H41" s="57">
+      <c r="H41" s="72">
         <v>21.744497188744</v>
       </c>
     </row>
@@ -10699,50 +10923,50 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E42" s="51">
+      <c r="E42" s="66">
         <v>2025</v>
       </c>
-      <c r="F42" s="53">
+      <c r="F42" s="68">
         <v>10512.61</v>
       </c>
-      <c r="G42" s="55">
+      <c r="G42" s="70">
         <v>1010.9</v>
       </c>
-      <c r="H42" s="57">
+      <c r="H42" s="72">
         <v>10.3992580868533</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="65" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="65" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA DEL RIO GRANDE</t>
-        </is>
-      </c>
-      <c r="E43" s="52">
+      <c r="D43" s="65" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RIO GRANDE</t>
+        </is>
+      </c>
+      <c r="E43" s="67">
         <v>2025</v>
       </c>
-      <c r="F43" s="54">
+      <c r="F43" s="69">
         <v>249792.76</v>
       </c>
-      <c r="G43" s="56">
+      <c r="G43" s="71">
         <v>9071.41</v>
       </c>
-      <c r="H43" s="58">
+      <c r="H43" s="73">
         <v>27.5362661372378</v>
       </c>
     </row>
@@ -10758,29 +10982,29 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="75" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="75" t="inlineStr">
         <is>
           <t>anio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="75" t="inlineStr">
         <is>
           <t>total_especies</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="75" t="inlineStr">
         <is>
           <t>participacion_pecuario_prov_pct</t>
         </is>
@@ -10878,23 +11102,23 @@
   <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="77" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="77" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="77" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
